--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
@@ -743,10 +743,10 @@
         <v>18.2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>17</v>
@@ -755,48 +755,52 @@
         <v>6.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="n"/>
+      <c r="L4" s="3" t="n">
+        <v>16.1</v>
+      </c>
       <c r="M4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O4" s="3" t="n">
-        <v>84</v>
+        <v>845</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q4" s="8" t="n">
-        <v>227.8</v>
+      <c r="Q4" s="3" t="n">
+        <v>117.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>651.3</v>
+      <c r="S4" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>54.8</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V4" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V4" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>56.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>13.6</v>
@@ -816,7 +820,7 @@
       </c>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n">
-        <v>28.4</v>
+        <v>8.4</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>17.6</v>
@@ -825,7 +829,7 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.8</v>
@@ -837,52 +841,52 @@
         <v>9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>16.9</v>
+        <v>11.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>823.5</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q5" s="8" t="n">
-        <v>28.4</v>
+        <v>3.9</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>48.4</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>21.8</v>
+      <c r="S5" s="8" t="n">
+        <v>41.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U5" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>18.2</v>
+        <v>1.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -905,16 +909,16 @@
         <v>17.8</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>92.8</v>
+        <v>32.1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>17.6</v>
+        <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>12.6</v>
@@ -922,9 +926,11 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n"/>
+      <c r="L6" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="M6" s="3" t="n">
-        <v>162.4</v>
+        <v>1.8</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>18.2</v>
@@ -933,10 +939,10 @@
         <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>481.1</v>
+        <v>47.1</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>21.8</v>
@@ -948,18 +954,20 @@
         <v>56.4</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="Y6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n">
+        <v>57.8</v>
+      </c>
       <c r="Z6" s="3" t="n">
         <v>14</v>
       </c>
@@ -984,57 +992,59 @@
         <v>17.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>24.1</v>
+        <v>14.1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>8.6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K7" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>109.2</v>
+      <c r="K7" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54621561
+81
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>28341.2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>42.6</v>
+        <v>4.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="W7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1063,37 +1073,39 @@
       <c r="D8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>17.8</v>
+      <c r="E8" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>20.9</v>
+        <v>23.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="I8" s="3" t="n"/>
+      <c r="I8" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="J8" s="3" t="n">
-        <v>19.2</v>
+        <v>1.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>18.6</v>
       </c>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>81.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>30.6</v>
@@ -1102,15 +1114,19 @@
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T8" s="3" t="n"/>
-      <c r="U8" s="3" t="n"/>
+        <v>1.7</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="V8" s="3" t="n">
-        <v>25.8</v>
+        <v>29.8</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>19.4</v>
+        <v>1.4</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>18.7</v>
@@ -1119,7 +1135,7 @@
         <v>56.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>1194.4</v>
+        <v>14.4</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1138,36 +1154,43 @@
       <c r="D9" s="3" t="n">
         <v>145.8</v>
       </c>
-      <c r="E9" s="3" t="n"/>
+      <c r="E9" s="3" t="n">
+        <v>88.7</v>
+      </c>
       <c r="F9" s="3" t="n">
-        <v>117.1</v>
+        <v>0.7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>63.7</v>
+        <v>63</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>134.6</v>
+        <v>34.1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>256.4</v>
+        <v>56.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0.4</v>
+        <v>83.2</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1717
+20 4
+89 8 6
+</t>
+        </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>18.5</v>
+        <v>84.7</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
@@ -1176,31 +1199,31 @@
         <v>145.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>10.6</v>
+        <v>196.1</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>122.6</v>
+        <v>12.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>288.1</v>
+        <v>51</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>2938.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>73.5</v>
+        <v>13.4</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>970.1</v>
+        <v>914.4</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>95.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1.4</v>
+        <v>194.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1217,31 +1240,31 @@
       </c>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n">
-        <v>29.2</v>
+        <v>2.2</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>7.3</v>
+        <v>23.4</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.5</v>
+        <v>46.4</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>18.6</v>
+        <v>21.8</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1250,10 +1273,10 @@
         <v>18</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>84.7</v>
+        <v>820.1</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>29.2</v>
@@ -1262,28 +1285,28 @@
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>20.5</v>
+        <v>0.6</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>51</v>
+        <v>4.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.4</v>
+        <v>1.4</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>13.4</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1300,69 +1323,73 @@
       </c>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n">
-        <v>33.4</v>
+        <v>6.4</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16.8</v>
+        <v>4.6</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G11" s="3" t="n"/>
+        <v>23.1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>716.1</v>
+      </c>
       <c r="H11" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="I11" s="3" t="n"/>
+      <c r="I11" s="3" t="n">
+        <v>34.1</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>18</v>
+        <v>86.09999999999999</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>890.1</v>
+        <v>89</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>44.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>6.8</v>
+        <v>48.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>900.6</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>18.4</v>
+        <v>700.6</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>48.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>47.5</v>
+        <v>5.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>20.2</v>
+        <v>1.1</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>600.1</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>13</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1385,39 +1412,39 @@
         <v>18</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>16.4</v>
+        <v>1.4</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>6.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>21.8</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>49.9</v>
+        <v>14.6</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>17.4</v>
+        <v>1.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>89</v>
+        <v>23.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" s="8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q12" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1427,7 +1454,7 @@
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>57.1</v>
+        <v>58</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>16.2</v>
@@ -1436,13 +1463,13 @@
         <v>25.6</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>600.1</v>
+        <v>6</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>13</v>
@@ -1462,68 +1489,70 @@
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>17.2</v>
+        <v>1.4</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.4</v>
+        <v>1.4</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L13" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="M13" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>83.5</v>
+        <v>24.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>66</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>19.9</v>
+        <v>1.9</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>58</v>
+        <v>5.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>17.4</v>
+      <c r="W13" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>10.6</v>
@@ -1543,12 +1572,14 @@
       </c>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n">
-        <v>27.4</v>
+        <v>17.4</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="G14" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
@@ -1556,55 +1587,55 @@
         <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>19</v>
+        <v>10.9</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M14" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>74.5</v>
+        <v>213.4</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>26.8</v>
+        <v>46.2</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="S14" s="8" t="n">
-        <v>118.2</v>
+      <c r="S14" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>21.5</v>
+        <v>52.1</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>17</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>23.6</v>
+        <v>50.1</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X14" s="3" t="n">
-        <v>1.9</v>
+      <c r="X14" s="8" t="n">
+        <v>39.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>61.8</v>
+        <v>6</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1624,31 +1655,35 @@
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n">
-        <v>28.8</v>
+        <v>18.8</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>11</v>
+        <v>23.6</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>10.2</v>
+        <v>1.6</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42292792
+64
+</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>64.59999999999999</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>18.6</v>
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>220.5</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>16.8</v>
@@ -1660,22 +1695,22 @@
         <v>84</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>13.4</v>
+        <v>72.2</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>21.2</v>
+      <c r="R15" s="8" t="n">
+        <v>12.6</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>22.1</v>
+        <v>111.9</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>25.4</v>
@@ -1687,10 +1722,10 @@
         <v>17.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>114.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1707,17 +1742,19 @@
       </c>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E16" s="3" t="n"/>
+        <v>38.8</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="F16" s="3" t="n">
-        <v>193.9</v>
+        <v>13.9</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>249.8</v>
+        <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>20.6</v>
@@ -1726,52 +1763,52 @@
         <v>50.6</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>220.3</v>
+        <v>18.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>84</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>72.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>138.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>102.1</v>
+        <v>132.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>28.8</v>
+        <v>988.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>211.9</v>
+        <v>53.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>814.4</v>
+        <v>813.4</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>122.8</v>
+        <v>12.8</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>933.5</v>
+        <v>93.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>55</v>
+        <v>202.5</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1794,22 +1831,26 @@
         <v>17.8</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>113.9</v>
+        <v>2.8</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>6.1</v>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+61
+</t>
+        </is>
       </c>
       <c r="J17" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>18.6</v>
@@ -1817,42 +1858,44 @@
       <c r="M17" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="3" t="n"/>
+      <c r="N17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>84</v>
+        <v>284.6</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R17" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R17" s="8" t="n">
         <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>53.2</v>
+        <v>482.1</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>17.2</v>
+        <v>1.2</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>19.7</v>
+        <v>1.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1869,73 +1912,73 @@
       </c>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n">
-        <v>305.5</v>
+        <v>9.5</v>
       </c>
       <c r="E18" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>13.6</v>
-      </c>
       <c r="H18" s="3" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>18.6</v>
+        <v>43.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.6</v>
+        <v>164.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.1</v>
+        <v>1</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>12.1</v>
+        <v>118.2</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>504.1</v>
+        <v>2.8</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>41.5</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>24.8</v>
+        <v>0.1</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>432.1</v>
+        <v>46.8</v>
       </c>
       <c r="U18" s="3" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>6.2</v>
       </c>
-      <c r="V18" s="3" t="n">
-        <v>864.1</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>20.2</v>
-      </c>
       <c r="X18" s="3" t="n">
-        <v>10.1</v>
+        <v>109.1</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>580.1</v>
+        <v>8</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>9.4</v>
+        <v>19.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1951,72 +1994,72 @@
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="8" t="n">
-        <v>29.6</v>
+      <c r="D19" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>17.6</v>
+        <v>13.1</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>0.4</v>
+        <v>13.5</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
+        <v>1.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O19" s="3" t="n">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="R19" s="8" t="n">
-        <v>209.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>19.4</v>
+        <v>1.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>46.8</v>
+        <v>4.5</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2033,40 +2076,40 @@
       </c>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>23.1</v>
+        <v>12.4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>11.9</v>
+        <v>8.6</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>71.90000000000001</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>12.6</v>
+        <v>1.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>18.1</v>
+        <v>1.4</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>881</v>
+        <v>80.8</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.8</v>
@@ -2078,28 +2121,28 @@
         <v>21.8</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>148.5</v>
+        <v>56</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>26.4</v>
+        <v>465.4</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>50.5</v>
+        <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58.8</v>
+        <v>8</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2116,61 +2159,61 @@
       </c>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>417</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>26.5</v>
-      </c>
       <c r="R21" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.8</v>
+        <v>1.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v>15.9</v>
+        <v>68.3</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>18.6</v>
@@ -2179,7 +2222,7 @@
         <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2205,67 +2248,67 @@
         <v>17.6</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>17</v>
+        <v>10.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>16.6</v>
+        <v>4.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>18.8</v>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.2</v>
+        <v>23</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>188</v>
+        <v>2.8</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>19.8</v>
+        <v>12.5</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>68.3</v>
+        <v>267.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v>19.6</v>
+        <v>39</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>16.8</v>
+        <v>25.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>16</v>
+        <v>726.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>25.4</v>
+        <v>35.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2288,67 +2331,65 @@
         <v>99.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>110.8</v>
+        <v>117.6</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>568.2</v>
+        <v>56.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>84.8</v>
+        <v>34.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.2</v>
+        <v>32.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>52.9</v>
+        <v>5.9</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>93</v>
+        <v>1.6</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>285</v>
+        <v>185</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>18.8</v>
+        <v>357.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>126.8</v>
+        <v>0.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>740.8</v>
+        <v>740.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>103.9</v>
+        <v>113.4</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>111.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>96.7</v>
+        <v>68.3</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>975.1</v>
+        <v>175.1</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>95.59999999999999</v>
-      </c>
+        <v>1238.5</v>
+      </c>
+      <c r="W23" s="3" t="n"/>
       <c r="X23" s="3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>30.5</v>
+        <v>3152.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>52.8</v>
+        <v>62.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2365,73 +2406,73 @@
       </c>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n">
-        <v>29.1</v>
+        <v>2.1</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>17.6</v>
+      <c r="F24" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>11.7</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>52.9</v>
+        <v>6.6</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>6.8</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>28.1</v>
+        <v>0.8</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>20.7</v>
+        <v>0.3</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>53.5</v>
+        <v>3.5</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>24.7</v>
+        <v>4.7</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>19.1</v>
+        <v>3.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.9</v>
+        <v>0.8</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.8</v>
+        <v>121.6</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2447,21 +2488,23 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="8" t="n">
+        <v>45.6</v>
+      </c>
       <c r="E25" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>18.8</v>
+        <v>4.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>26.1</v>
+        <v>16.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.2</v>
@@ -2470,46 +2513,46 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>16.2</v>
+        <v>47.1</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>18.4</v>
+        <v>16.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>83.5</v>
+        <v>356.4</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>34.1</v>
+        <v>54.1</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>19.4</v>
+        <v>0.8</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>605.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>0.2</v>
+        <v>138.1</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>13.9</v>
+        <v>438.1</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>88.8</v>
+        <v>8.9</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
@@ -2529,43 +2572,43 @@
       </c>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n">
-        <v>28.8</v>
+        <v>68.8</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>48.4</v>
+      <c r="F26" s="8" t="n">
+        <v>30.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16</v>
+        <v>11.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>304.1</v>
+        <v>0.1</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>16.8</v>
+      <c r="M26" s="8" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>16.1</v>
+        <v>18.9</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
@@ -2574,7 +2617,7 @@
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>8</v>
+        <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>52.2</v>
@@ -2582,20 +2625,20 @@
       <c r="U26" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V26" s="3" t="n">
-        <v>24.4</v>
+      <c r="V26" s="8" t="n">
+        <v>4494.4</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>28.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2612,42 +2655,46 @@
       </c>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>21.4</v>
-      </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>465.4</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>194.6</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>27.4</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>20.8</v>
@@ -2658,7 +2705,7 @@
       <c r="T27" s="3" t="n">
         <v>56.7</v>
       </c>
-      <c r="U27" s="3" t="n">
+      <c r="U27" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="V27" s="3" t="n">
@@ -2668,7 +2715,7 @@
         <v>19.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>64</v>
@@ -2691,71 +2738,73 @@
       </c>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>18</v>
+        <v>14.4</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>87.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>22.8</v>
+        <v>2.1</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>16</v>
+      <c r="H28" s="8" t="n">
+        <v>60.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>24</v>
+        <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="L28" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="O28" s="3" t="n"/>
+      <c r="M28" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="P28" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>27.4</v>
+        <v>22.4</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>20.7</v>
+        <v>0.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>95.59999999999999</v>
+        <v>56.1</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59</v>
+        <v>52.5</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2775,10 +2824,10 @@
         <v>26.8</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>17.9</v>
+        <v>1.4</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>22.9</v>
+        <v>2.1</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>9.4</v>
@@ -2787,22 +2836,22 @@
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.4</v>
+        <v>424.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>19.9</v>
+        <v>12.1</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>89</v>
@@ -2820,22 +2869,22 @@
         <v>19.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>29.2</v>
+        <v>5.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="V29" s="8" t="n">
-        <v>229.6</v>
+      <c r="V29" s="3" t="n">
+        <v>43.6</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>19.6</v>
+        <v>12.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>66.2</v>
+        <v>6.2</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>9.800000000000001</v>
@@ -2855,71 +2904,73 @@
       </c>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n">
-        <v>133.4</v>
+        <v>1353.2</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>47.4</v>
+        <v>31.6</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>33</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>9.1</v>
+        <v>41.7</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>2.8</v>
+        <v>89</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>115.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>139</v>
+        <v>139.1</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>102.4</v>
+        <v>19.6</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>298</v>
+        <v>5.5</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="V30" s="3" t="n"/>
+        <v>28.1</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>118.2</v>
+      </c>
       <c r="W30" s="3" t="n">
-        <v>95</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>5.6</v>
+        <v>34.6</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>45.1</v>
+        <v>4981.1</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2936,71 +2987,71 @@
       </c>
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="n">
-        <v>26.6</v>
+        <v>2.6</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F31" s="8" t="n">
-        <v>9.6</v>
+      <c r="F31" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H31" s="8" t="n">
-        <v>10.6</v>
+      <c r="H31" s="3" t="n">
+        <v>876.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="n">
+        <v>7.1</v>
+      </c>
       <c r="L31" s="3" t="n">
-        <v>944.1</v>
+        <v>94</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="O31" s="3" t="n"/>
       <c r="P31" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.4</v>
+        <v>6.4</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>20.4</v>
+        <v>2.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>20.4</v>
+        <v>2.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.4</v>
+        <v>14.2</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>23.6</v>
+        <v>43.6</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>19.8</v>
+        <v>8.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>67.2</v>
+        <v>0.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3017,7 +3068,7 @@
       </c>
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n">
-        <v>26.2</v>
+        <v>4.2</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>17.6</v>
@@ -3029,49 +3080,49 @@
         <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>26.7</v>
+        <v>1.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>482.4</v>
+        <v>1.8</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>18.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>92.40000000000001</v>
+        <v>28.5</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>19.8</v>
+        <v>1.2</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>56.8</v>
+        <v>6.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>18.8</v>
@@ -3080,7 +3131,7 @@
         <v>19.5</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>71</v>
+        <v>21.8</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>8</v>
@@ -3103,25 +3154,25 @@
         <v>26.6</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>17.2</v>
+        <v>1.2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>21.9</v>
+        <v>1.9</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.4</v>
@@ -3130,41 +3181,43 @@
         <v>565.1</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>11.8</v>
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>84</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q33" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V33" s="3" t="n"/>
+      <c r="V33" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="W33" s="3" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>75</v>
+        <v>16.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3180,56 +3233,56 @@
         </is>
       </c>
       <c r="C34" s="3" t="n"/>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>21.9</v>
+        <v>23.1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>57.2</v>
+        <v>57.6</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>15.3</v>
@@ -3238,16 +3291,16 @@
         <v>24.6</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>10.2</v>
+        <v>16.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3264,71 +3317,73 @@
       </c>
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>23.1</v>
+        <v>14.1</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="H35" s="8" t="n">
-        <v>17</v>
+      <c r="H35" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="N35" s="3" t="n"/>
+      <c r="N35" s="3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>900.6</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>24.2</v>
+        <v>4.2</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>20.4</v>
+        <v>6.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>20.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>86.5</v>
+        <v>6</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>3.2</v>
+        <v>32.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3344,61 +3399,63 @@
         </is>
       </c>
       <c r="C36" s="3" t="n"/>
-      <c r="D36" s="8" t="n">
-        <v>28.6</v>
+      <c r="D36" s="3" t="n">
+        <v>48.6</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>20.9</v>
+        <v>2.6</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>10.8</v>
+        <v>11.8</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N36" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="N36" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>87</v>
+        <v>83.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>21.8</v>
+        <v>61.8</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="V36" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>20.4</v>
+      </c>
       <c r="W36" s="3" t="n">
         <v>18.8</v>
       </c>
@@ -3406,10 +3463,10 @@
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.2</v>
+        <v>35.2</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3426,25 +3483,25 @@
       </c>
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n">
-        <v>112.8</v>
+        <v>132.8</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>88.2</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>23.2</v>
+        <v>2.6</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>45.6</v>
+        <v>456.1</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>5.9</v>
+        <v>20.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>31.2</v>
+        <v>3.1</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>18.6</v>
@@ -3453,41 +3510,43 @@
         <v>18.6</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>846.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>595.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1139.5</v>
+        <v>87</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>131.8</v>
+        <v>134.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>102.2</v>
+        <v>1922.8</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="T37" s="3" t="n"/>
+        <v>7.7</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>56.4</v>
+      </c>
       <c r="U37" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>709.6</v>
+        <v>713.6</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>101.6</v>
+        <v>18.8</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>386.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>7.9</v>
+        <v>86.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3507,70 +3566,82 @@
       </c>
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="n">
-        <v>26.8</v>
+        <v>16.8</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>17.6</v>
+        <v>1.6</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G38" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G38" s="8" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>895</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>20.9</v>
+      <c r="H38" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+9
+</t>
+        </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.7</v>
+        <v>27.3</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>16.5</v>
+        <v>1.5</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>737.8</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q38" s="3" t="n">
-        <v>26.8</v>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+248
+</t>
+        </is>
       </c>
       <c r="R38" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>28.3</v>
+        <v>0.6</v>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+203
+</t>
+        </is>
       </c>
       <c r="T38" s="3" t="n">
-        <v>5.7</v>
+        <v>57.8</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>14.9</v>
+        <v>4.7</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>11.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>20.3</v>
+        <v>2.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.9</v>
+        <v>0.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.2</v>
@@ -3592,17 +3663,17 @@
       <c r="D39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E39" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>22.6</v>
+      <c r="F39" s="3" t="n">
+        <v>42.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.2</v>
@@ -3611,52 +3682,52 @@
         <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>9.6</v>
+        <v>27.3</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="M39" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R39" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>2208.4</v>
-      </c>
       <c r="S39" s="3" t="n">
-        <v>19.8</v>
+        <v>13.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>114.9</v>
+        <v>1.9</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>39.4</v>
+        <v>35.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>28.5</v>
+        <v>19.6</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>181.1</v>
+        <v>64.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3679,67 +3750,67 @@
         <v>18.4</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>71.8</v>
+        <v>2.5</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>16.8</v>
+        <v>1.8</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5.4</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>194.1</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N40" s="8" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="P40" s="8" t="n">
-        <v>126.2</v>
+        <v>84</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>20</v>
+        <v>6.6</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>61.6</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>56.8</v>
+        <v>5.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>28.8</v>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>20.1</v>
+        <v>11.6</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>81.5</v>
+        <v>14.4</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3756,69 +3827,71 @@
       </c>
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E41" s="8" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E41" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F41" s="3" t="n"/>
+      <c r="F41" s="3" t="n">
+        <v>21.3</v>
+      </c>
       <c r="G41" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>59.5</v>
+        <v>1.8</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>17.2</v>
+      <c r="M41" s="8" t="n">
+        <v>72.09999999999999</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>15.9</v>
+        <v>18.7</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>81</v>
+        <v>840.1</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>22.6</v>
+        <v>0.3</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.9</v>
+        <v>57.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>19.6</v>
+        <v>14.4</v>
       </c>
       <c r="V41" s="3" t="n"/>
       <c r="W41" s="3" t="n">
-        <v>16.8</v>
+        <v>18.6</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>19.6</v>
+        <v>76.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
+        <v>81.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>14.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3834,47 +3907,47 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>22.9</v>
+        <v>18.1</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>70.8</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>14</v>
+        <v>1.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>16.4</v>
+        <v>23.5</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>13</v>
+        <v>24.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>28.6</v>
+        <v>0.3</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>21</v>
@@ -3883,22 +3956,26 @@
         <v>20.4</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="V42" s="3" t="n"/>
+      <c r="V42" s="3" t="n">
+        <v>6.9</v>
+      </c>
       <c r="W42" s="3" t="n">
-        <v>20</v>
+        <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>19.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3917,69 +3994,71 @@
         <v>30.4</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.1</v>
+        <v>4.5</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G43" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G43" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J43" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J43" s="3" t="n">
         <v>15</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.4</v>
+        <v>12.4</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
+        <v>1.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>85</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>4.9</v>
+        <v>28.6</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>0.6</v>
+        <v>30.6</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>20.6</v>
+        <v>21.8</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>18.9</v>
+        <v>2.9</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>142.6</v>
+        <v>42.6</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>26.4</v>
+        <v>6.9</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X43" s="8" t="n">
-        <v>427</v>
+      <c r="X43" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -3995,62 +4074,68 @@
       </c>
       <c r="C44" s="3" t="n"/>
       <c r="D44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="G44" s="3" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="H44" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>7.6</v>
+      <c r="I44" s="8" t="n">
+        <v>125.6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.3</v>
+        <v>1.3</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>18.8</v>
+        <v>11.8</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="P44" s="8" t="n">
-        <v>65</v>
+        <v>80</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>765</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>21.8</v>
+        <v>766.1</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>157.1</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>20.9</v>
+        <v>62.6</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="V44" s="8" t="n">
-        <v>14.8</v>
+      <c r="V44" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X44" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
@@ -4070,74 +4155,76 @@
       </c>
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="n">
-        <v>24.8</v>
+        <v>28.6</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>17.1</v>
+        <v>1.1</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>92.2</v>
+        <v>32.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>33.5</v>
+        <v>3.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.9</v>
+        <v>61.3</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>499.6</v>
+        <v>139.6</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>998.4</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>52.6</v>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+41 1
+</t>
+        </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>165</v>
+        <v>21.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>765</v>
+        <v>27.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>111.1</v>
+        <v>26.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>16.2</v>
+        <v>1.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>107.1</v>
+        <v>317.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>143.9</v>
+        <v>23.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>114.8</v>
+        <v>1.1</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>19.1</v>
+        <v>4</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>65.5</v>
+        <v>0.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>10.4</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4153,16 +4240,20 @@
       </c>
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>17.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+6
+</t>
+        </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4173,51 +4264,62 @@
       <c r="J46" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="L46" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>7.8</v>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+41 1
+</t>
+        </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>21.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>28.6</v>
+        <v>0.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>20.1</v>
+        <v>157.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>15.8</v>
+        <v>1.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>917.9</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2919292795
+24
+12
+</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>19.1</v>
+        <v>1.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>65.5</v>
+        <v>0.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>10.4</v>
+        <v>0.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
@@ -735,37 +735,61 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="n">
+        <v>5.4</v>
+      </c>
       <c r="D4" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+        <v>27.8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="G4" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="H4" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="M4" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O4" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="P4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="n">
+        <v>513.9</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>27.8</v>
+        <v>21.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" s="3" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
@@ -785,32 +809,56 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="G5" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>83</v>
+      </c>
       <c r="P5" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q5" s="3" t="inlineStr"/>
+        <v>12.7</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>28.4</v>
+      </c>
       <c r="R5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="T5" s="3" t="n">
-        <v>54.8</v>
+        <v>56.8</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>16.8</v>
@@ -818,7 +866,7 @@
       <c r="V5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -844,44 +892,62 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="E6" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="8" t="n">
+      <c r="F6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>7.4</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>28.6</v>
+      </c>
       <c r="R6" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S6" s="3" t="inlineStr"/>
+        <v>21.8</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="T6" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U6" s="8" t="n">
+        <v>656.4</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>20</v>
@@ -910,49 +976,71 @@
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+        <v>30.4</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H7" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="L7" s="8" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>484.1</v>
+      </c>
       <c r="N7" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O7" s="3" t="inlineStr"/>
+        <v>19.2</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>89</v>
+      </c>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>18.5</v>
+      </c>
       <c r="T7" s="3" t="n">
-        <v>146.4</v>
+        <v>142.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>27.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -969,47 +1057,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>13.8</v>
+      </c>
       <c r="H8" s="8" t="n">
-        <v>95.40000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>81</v>
+      </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="n">
+        <v>21.2</v>
+      </c>
       <c r="S8" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>24.2</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>25.8</v>
+      </c>
       <c r="W8" s="3" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>19.3</v>
+        <v>18.7</v>
       </c>
       <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="n">
@@ -1030,67 +1132,73 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="n">
-        <v>145.8</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+        <v>142.8</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>115.2</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>27.1</v>
+        <v>57.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>824.4</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>565.4</v>
+        <v>26.6</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>34.1</v>
+        <v>91.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
+        <v>82.2</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>89.8</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>122.9</v>
+        <v>42.3</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1943.8</v>
+        <v>142.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1096</v>
+        <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>19.7</v>
+        <v>100.8</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>201.1</v>
+        <v>2099.1</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.2</v>
+        <v>992.6</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>911.4</v>
+        <v>11.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>18.7</v>
+        <v>19.1</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0.4</v>
+        <v>229.9</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>14.4</v>
+        <v>615</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1107,69 +1215,73 @@
       </c>
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="n">
-        <v>145.8</v>
+        <v>29.2</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>17.7</v>
+        <v>11.7</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>27.1</v>
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>824.4</v>
+        <v>16.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>34.1</v>
+        <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>565.4</v>
+        <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>18.6</v>
+        <v>0.5</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>34.1</v>
+        <v>18</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>122.9</v>
+        <v>84.7</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q10" s="8" t="n">
-        <v>943.8</v>
-      </c>
-      <c r="R10" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="S10" s="8" t="n">
-        <v>102.6</v>
+        <v>7.2</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>163.1</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>29461</v>
+        <v>51</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>12.2</v>
+        <v>25.4</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>911.4</v>
-      </c>
-      <c r="X10" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y10" s="3" t="n">
-        <v>0.4</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>165</v>
+        <v>13.9</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1185,57 +1297,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
+      <c r="D11" s="8" t="n">
+        <v>28.4</v>
+      </c>
       <c r="E11" s="3" t="n">
-        <v>17.7</v>
+        <v>16.8</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
+        <v>22.6</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H11" s="3" t="n">
-        <v>16.8</v>
+        <v>13.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>16.9</v>
+        <v>5.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O11" s="3" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
+        <v>890.9</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q11" s="8" t="n">
-        <v>29.2</v>
+        <v>18.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="n">
-        <v>19.9</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="W11" s="3" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1249,65 +1367,75 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>28.2</v>
+      </c>
       <c r="E12" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>182</v>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="Q12" s="3" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>18.4</v>
+        <v>21.6</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>2941.2</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>19.1</v>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>28.9</v>
+        <v>60</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>13.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1322,59 +1450,77 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="E13" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="8" t="n">
-        <v>11.6</v>
+        <v>1.7</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>41.2</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J13" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>182</v>
+        <v>9.6</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
+        <v>283.5</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>41.4</v>
+      </c>
       <c r="Q13" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="R13" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>18.4</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>2941.2</v>
-      </c>
-      <c r="U13" s="3" t="inlineStr"/>
+        <v>51.1</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="V13" s="8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W13" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W13" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="X13" s="3" t="inlineStr"/>
-      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>60</v>
+      </c>
       <c r="Z13" s="3" t="n">
-        <v>13.8</v>
+        <v>1.3</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1390,58 +1536,74 @@
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="H14" s="3" t="n">
-        <v>16.4</v>
+        <v>27.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>191.6</v>
+        <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="n">
-        <v>19.2</v>
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>87.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="8" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>24.9</v>
+        <v>74.5</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>51.1</v>
+        <v>58</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>14</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
+        <v>22.6</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="X14" s="3" t="n">
-        <v>19.1</v>
+        <v>16.8</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>13.8</v>
+        <v>10.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1457,52 +1619,72 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="F15" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="I15" s="3" t="n">
-        <v>16</v>
+        <v>6.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="N15" s="3" t="n">
-        <v>16.9</v>
+        <v>18.1</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>28.8</v>
+      </c>
       <c r="R15" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S15" s="3" t="inlineStr"/>
+        <v>21.2</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>20.7</v>
+      </c>
       <c r="T15" s="3" t="n">
-        <v>58</v>
+        <v>52.1</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr"/>
+        <v>25.4</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y15" s="3" t="n">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>10.6</v>
+        <v>114.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1519,45 +1701,73 @@
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+        <v>1198.8</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1113.9</v>
+      </c>
       <c r="G16" s="3" t="n">
-        <v>1191</v>
+        <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>117.6</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>900.6</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>980.8</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>2281.2</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>104.1</v>
+      </c>
       <c r="S16" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>86.2</v>
+      </c>
       <c r="V16" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W16" s="3" t="inlineStr"/>
+        <v>152.8</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>94.5</v>
+      </c>
       <c r="X16" s="3" t="n">
-        <v>187.8</v>
+        <v>92.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>25</v>
+        <v>304.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>114.6</v>
+        <v>14.1</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1572,69 +1782,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="8" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>134.4</v>
+      <c r="C17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>49.8</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>10.6</v>
+        <v>16.8</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>6.1</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>10.1</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="M17" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O17" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>128.2</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>98.8</v>
+        <v>13.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>266.2</v>
-      </c>
-      <c r="U17" s="3" t="inlineStr"/>
-      <c r="V17" s="8" t="n">
-        <v>22.8</v>
+        <v>52.2</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>148.1</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>99.3</v>
+        <v>12</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>302</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>61</v>
+        <v>12.2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1649,54 +1865,74 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="n">
-        <v>27.8</v>
+      <c r="C18" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>80.40000000000001</v>
       </c>
       <c r="E18" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="N18" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>14.6</v>
+      </c>
       <c r="Q18" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="inlineStr"/>
+        <v>20.4</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V18" s="3" t="n">
-        <v>24.6</v>
+        <v>26.4</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>12.2</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1712,47 +1948,71 @@
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="n">
-        <v>12.5</v>
+        <v>29.6</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="K19" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="T19" s="3" t="n">
         <v>46.8</v>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="n">
-        <v>2948.1</v>
-      </c>
-      <c r="U19" s="3" t="inlineStr"/>
-      <c r="V19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>26.1</v>
+      </c>
       <c r="W19" s="3" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y19" s="3" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>34</v>
+      </c>
       <c r="Z19" s="3" t="n">
-        <v>1149.5</v>
+        <v>19.9</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -1768,40 +2028,72 @@
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>24.4</v>
+      </c>
       <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="H20" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>7.9</v>
+      </c>
       <c r="J20" s="3" t="n">
-        <v>17.8</v>
+        <v>12.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="T20" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="U20" s="3" t="inlineStr"/>
-      <c r="V20" s="3" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr"/>
+        <v>48.8</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>20.2</v>
+      </c>
       <c r="X20" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="n">
+        <v>58</v>
+      </c>
       <c r="Z20" s="3" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -1817,38 +2109,72 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="8" t="n">
+      <c r="D21" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>12.6</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>948.5</v>
-      </c>
-      <c r="U21" s="3" t="inlineStr"/>
-      <c r="V21" s="3" t="inlineStr"/>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr"/>
-      <c r="Y21" s="3" t="inlineStr"/>
-      <c r="Z21" s="3" t="n">
-        <v>114.9</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -1864,42 +2190,72 @@
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>7.4</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="T22" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="U22" s="3" t="inlineStr"/>
+        <v>68.3</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="V22" s="3" t="n">
-        <v>24.4</v>
+        <v>19.6</v>
       </c>
       <c r="W22" s="8" t="n">
-        <v>18.6</v>
+        <v>16.8</v>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
       <c r="Y22" s="3" t="n">
-        <v>39</v>
+        <v>16.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>12.6</v>
+        <v>5.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -1914,51 +2270,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>195.6</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="G23" s="3" t="n">
-        <v>10.8</v>
+        <v>26.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+        <v>84.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>92.09999999999999</v>
+      </c>
       <c r="J23" s="3" t="n">
-        <v>1.4</v>
+        <v>52.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
+        <v>926.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>140.4</v>
+      </c>
       <c r="R23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="S23" s="3" t="inlineStr"/>
+        <v>103.4</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>1180.4</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="U23" s="3" t="inlineStr"/>
+        <v>267.9</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>91.90000000000001</v>
+      </c>
       <c r="V23" s="3" t="n">
-        <v>19.6</v>
+        <v>123.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="X23" s="3" t="inlineStr"/>
+        <v>20.6</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>41.8</v>
+      </c>
       <c r="Y23" s="3" t="n">
-        <v>16</v>
+        <v>2216.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>5.4</v>
+        <v>24.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -1973,71 +2355,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="8" t="n">
-        <v>945.6</v>
+      <c r="C24" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>29.1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>31.1</v>
+        <v>6.6</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>20.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>85.40000000000001</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>156.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>80.40000000000001</v>
+        <v>28.1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>1267.8</v>
+        <v>53.5</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="W24" s="8" t="n">
-        <v>20.6</v>
+        <v>18.5</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>94.8</v>
+        <v>18.9</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>302</v>
+        <v>61</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>52.8</v>
+        <v>12.6</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2052,58 +2438,70 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="n">
+        <v>81.5</v>
+      </c>
       <c r="D25" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H25" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>6.6</v>
+        <v>19.6</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>20.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L25" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>82.90000000000001</v>
+      </c>
       <c r="P25" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>28.1</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>221.8</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>20.7</v>
+        <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr"/>
-      <c r="W25" s="3" t="n">
-        <v>19.1</v>
+        <v>20.9</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>86.40000000000001</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="inlineStr"/>
-      <c r="Z25" s="3" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2117,46 +2515,78 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>10.2</v>
+      </c>
       <c r="H26" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J26" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr"/>
+        <v>82.40000000000001</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="M26" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="3" t="inlineStr"/>
-      <c r="P26" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="Q26" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R26" s="3" t="inlineStr"/>
+        <v>28.8</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>21.2</v>
+      </c>
       <c r="S26" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>13.8</v>
+        <v>12.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="V26" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>29.4</v>
+      </c>
       <c r="W26" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
-      <c r="Y26" s="3" t="inlineStr"/>
-      <c r="Z26" s="3" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>112.8</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2170,46 +2600,70 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="G27" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="I27" s="3" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M27" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="R27" s="3" t="inlineStr"/>
+      <c r="N27" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="S27" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>12.2</v>
+        <v>56.9</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V27" s="3" t="inlineStr"/>
-      <c r="W27" s="3" t="inlineStr"/>
-      <c r="X27" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="Y27" s="3" t="inlineStr"/>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2226,37 +2680,67 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
+        <v>9.4</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="I28" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
-      <c r="O28" s="3" t="inlineStr"/>
-      <c r="P28" s="3" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>5294</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="Q28" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R28" s="3" t="inlineStr"/>
-      <c r="S28" s="3" t="inlineStr"/>
-      <c r="T28" s="3" t="inlineStr"/>
+        <v>21.4</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>56.7</v>
+      </c>
       <c r="U28" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V28" s="3" t="inlineStr"/>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
+        <v>15.8</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y28" s="3" t="inlineStr"/>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2273,37 +2757,75 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="8" t="n">
-        <v>16.6</v>
+      <c r="D29" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="O29" s="3" t="inlineStr"/>
-      <c r="P29" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q29" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
-      <c r="T29" s="3" t="inlineStr"/>
+        <v>25.6</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>659.5</v>
+      </c>
       <c r="U29" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X29" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="V29" s="3" t="inlineStr"/>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
-      <c r="Y29" s="3" t="inlineStr"/>
-      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2318,52 +2840,74 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="n">
+        <v>1952.4</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1816.8</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>131</v>
+      </c>
       <c r="I30" s="3" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr"/>
+        <v>2016.1</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>2681.4</v>
+      </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>18.6</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>17.4</v>
+        <v>836.5</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P30" s="3" t="inlineStr"/>
+        <v>420</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="Q30" s="3" t="n">
-        <v>125.6</v>
+        <v>132</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>19.8</v>
+        <v>1082</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="T30" s="3" t="inlineStr"/>
+        <v>102.2</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>298.9</v>
+      </c>
       <c r="U30" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="V30" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>1818.2</v>
+      </c>
       <c r="W30" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X30" s="3" t="inlineStr"/>
-      <c r="Y30" s="3" t="inlineStr"/>
+        <v>985.6</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>316.2</v>
+      </c>
       <c r="Z30" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>49.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2378,59 +2922,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="8" t="n">
-        <v>309.8</v>
-      </c>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="8" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>810</v>
+      <c r="C31" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>26.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>6.6</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="8" t="n">
+        <v>318.3</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr"/>
-      <c r="P31" s="8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" s="3" t="inlineStr"/>
-      <c r="T31" s="3" t="inlineStr"/>
+        <v>16.7</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>59.8</v>
+      </c>
       <c r="U31" s="3" t="n">
-        <v>30.4</v>
+        <v>19.2</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>1.5</v>
+        <v>23.6</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="X31" s="3" t="inlineStr"/>
-      <c r="Y31" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>69.2</v>
+      </c>
       <c r="Z31" s="3" t="n">
-        <v>249.8</v>
+        <v>10</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2445,54 +3005,76 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D32" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
+        <v>40.4</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>5.6</v>
+      </c>
       <c r="H32" s="3" t="n">
-        <v>26.8</v>
+        <v>15.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>94</v>
+        <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="W32" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M32" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
-      <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="inlineStr"/>
-      <c r="S32" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="8" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W32" s="3" t="inlineStr"/>
-      <c r="X32" s="3" t="inlineStr"/>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="X32" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -2506,62 +3088,74 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>23.1</v>
+      </c>
       <c r="G33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>16.9</v>
+        <v>2</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.4</v>
+        <v>17.4</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.7</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>86.8</v>
+        <v>84</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>2.7</v>
+        <v>28.6</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12.8</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -2578,39 +3172,69 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>17.4</v>
+        <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N34" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O34" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="3" t="inlineStr"/>
-      <c r="V34" s="3" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R34" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>284.6</v>
+      </c>
       <c r="W34" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X34" s="3" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="Y34" s="3" t="inlineStr"/>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -2626,41 +3250,71 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="F35" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr"/>
+        <v>21.8</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>5.2</v>
+      </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="8" t="n">
-        <v>17.2</v>
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N35" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="O35" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr"/>
-      <c r="T35" s="3" t="inlineStr"/>
-      <c r="U35" s="3" t="inlineStr"/>
-      <c r="V35" s="3" t="inlineStr"/>
-      <c r="W35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="W35" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="X35" s="3" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Y35" s="3" t="inlineStr"/>
       <c r="Z35" s="3" t="inlineStr"/>
@@ -2677,35 +3331,75 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="P36" s="3" t="inlineStr"/>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
-      <c r="T36" s="3" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>26.4</v>
+      </c>
       <c r="U36" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="V36" s="3" t="inlineStr"/>
-      <c r="W36" s="3" t="inlineStr"/>
+        <v>460.8</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="X36" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="Y36" s="3" t="inlineStr"/>
+        <v>20.8</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>86.5</v>
+      </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -2721,41 +3415,75 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="n">
+        <v>1120.8</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>808</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>21816.4</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>219.8</v>
+      </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>118.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>90.5</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>1082.2</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="3" t="inlineStr"/>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr"/>
+        <v>4920.8</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>1102.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>101.9</v>
+      </c>
       <c r="T37" s="3" t="n">
-        <v>26.4</v>
+        <v>288.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V37" s="3" t="inlineStr"/>
-      <c r="W37" s="3" t="inlineStr"/>
+        <v>14.1</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="X37" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Y37" s="3" t="inlineStr"/>
-      <c r="Z37" s="3" t="inlineStr"/>
+        <v>10.1</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>231.2</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2770,59 +3498,73 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="8" t="n">
-        <v>130.8</v>
-      </c>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="8" t="n">
-        <v>48.6</v>
+      <c r="D38" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>41.5</v>
+        <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="K38" s="8" t="n">
-        <v>15.4</v>
+        <v>6.9</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>95.09999999999999</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>866.1</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>92420.8</v>
-      </c>
-      <c r="O38" s="3" t="inlineStr"/>
+        <v>18.1</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
       <c r="P38" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="R38" s="8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="8" t="n">
-        <v>148.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W38" s="3" t="inlineStr"/>
-      <c r="X38" s="3" t="inlineStr"/>
-      <c r="Y38" s="3" t="inlineStr"/>
-      <c r="Z38" s="3" t="n">
-        <v>3931.2</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2836,55 +3578,75 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="E39" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="H39" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>42.1</v>
+        <v>46.8</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>19.4</v>
+      </c>
       <c r="M39" s="8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>898.6</v>
+      </c>
       <c r="P39" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.8</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S39" s="3" t="inlineStr"/>
+        <v>40.8</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>92.8</v>
+      </c>
       <c r="T39" s="3" t="n">
-        <v>57.7</v>
+        <v>86.8</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14.9</v>
+        <v>18.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>22</v>
+        <v>29.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X39" s="3" t="inlineStr"/>
-      <c r="Y39" s="3" t="inlineStr"/>
+        <v>10.6</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>69.8</v>
+      </c>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -2899,44 +3661,74 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J40" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O40" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="inlineStr"/>
-      <c r="R40" s="3" t="inlineStr"/>
-      <c r="S40" s="8" t="n">
-        <v>19.8</v>
+      <c r="P40" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>26</v>
+        <v>91.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V40" s="3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="W40" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="X40" s="8" t="n">
-        <v>18.6</v>
+      <c r="X40" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>69.2</v>
+        <v>81.5</v>
       </c>
       <c r="Z40" s="3" t="inlineStr"/>
       <c r="AA40" s="3" t="inlineStr">
@@ -2952,42 +3744,74 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="8" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
-      <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>840.1</v>
+        <v>81</v>
       </c>
       <c r="P41" s="3" t="inlineStr"/>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="W41" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X41" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>14.5</v>
+      </c>
       <c r="Y41" s="3" t="n">
-        <v>242.1</v>
-      </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+        <v>76.5</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3001,36 +3825,74 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="n">
+        <v>6.4</v>
+      </c>
       <c r="J42" s="8" t="n">
-        <v>191.6</v>
-      </c>
-      <c r="K42" s="3" t="inlineStr"/>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="3" t="inlineStr"/>
-      <c r="N42" s="3" t="inlineStr"/>
+        <v>11.6</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>8540.1</v>
-      </c>
-      <c r="P42" s="3" t="inlineStr"/>
-      <c r="Q42" s="3" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>28.6</v>
+      </c>
       <c r="R42" s="3" t="n">
         <v>21</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="3" t="inlineStr"/>
-      <c r="V42" s="3" t="inlineStr"/>
-      <c r="W42" s="3" t="inlineStr"/>
-      <c r="X42" s="3" t="inlineStr"/>
-      <c r="Y42" s="3" t="inlineStr"/>
-      <c r="Z42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3045,39 +3907,75 @@
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>18.5</v>
+      </c>
       <c r="H43" s="8" t="n">
-        <v>172.2</v>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="O43" s="3" t="inlineStr"/>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>9.4</v>
+      </c>
       <c r="R43" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S43" s="3" t="inlineStr"/>
-      <c r="T43" s="3" t="inlineStr"/>
-      <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="inlineStr"/>
+        <v>29.6</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y43" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z43" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -3092,36 +3990,42 @@
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="n">
-        <v>90</v>
+      <c r="D44" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="H44" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I44" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N44" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="N44" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="O44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="n">
+        <v>80.8</v>
+      </c>
       <c r="P44" s="3" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>30.6</v>
@@ -3129,14 +4033,24 @@
       <c r="R44" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="S44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
+      <c r="U44" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W44" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
@@ -3154,52 +4068,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>288.4</v>
+      </c>
       <c r="G45" s="3" t="n">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>33.5</v>
+        <v>22</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>61.8</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>9.4</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>109.6</v>
+        <v>1189.6</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="N45" s="3" t="inlineStr"/>
-      <c r="O45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="n">
+        <v>1102.7</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>17992.6</v>
+      </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1656</v>
-      </c>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
+        <v>1662</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T45" s="3" t="n">
-        <v>17.9</v>
+        <v>217.9</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>107.1</v>
       </c>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+      <c r="V45" s="3" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>322.8</v>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>169.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -3216,21 +4152,23 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="8" t="n">
-        <v>22.8</v>
+      <c r="D46" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>10.2</v>
@@ -3239,32 +4177,44 @@
       <c r="L46" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="M46" s="8" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>17.5</v>
+      </c>
       <c r="O46" s="3" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="n">
+        <v>27.6</v>
+      </c>
       <c r="R46" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="8" t="n">
+      <c r="S46" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="U46" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="n">
+        <v>23.8</v>
+      </c>
       <c r="W46" s="3" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>69.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>10.7</v>
+        <v>119.4</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
@@ -735,9 +735,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>5.4</v>
-      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
         <v>27.8</v>
       </c>
@@ -751,7 +749,7 @@
         <v>9.6</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>6.8</v>
@@ -762,9 +760,11 @@
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="8" t="n">
-        <v>16.8</v>
+      <c r="L4" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>6.8</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>18.1</v>
@@ -773,16 +773,16 @@
         <v>84</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>513.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>28.5</v>
+        <v>20.5</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>54.8</v>
@@ -833,11 +833,11 @@
       <c r="K5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L5" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>128.9</v>
+      <c r="L5" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>16.9</v>
@@ -845,9 +845,7 @@
       <c r="O5" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>28.4</v>
       </c>
@@ -858,7 +856,7 @@
         <v>21.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.8</v>
+        <v>58</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>16.8</v>
@@ -866,14 +864,14 @@
       <c r="V5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>56.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>13.6</v>
@@ -893,7 +891,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>17.8</v>
@@ -917,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>10.4</v>
+        <v>18.4</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>16.8</v>
@@ -929,7 +927,7 @@
         <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>28.6</v>
@@ -941,7 +939,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>656.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -981,9 +979,7 @@
       <c r="E7" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>24.1</v>
-      </c>
+      <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="n">
         <v>12.6</v>
       </c>
@@ -994,16 +990,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.5</v>
+        <v>14.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>118.6</v>
+        <v>18.6</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>484.1</v>
+        <v>7.4</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>19.2</v>
@@ -1011,7 +1007,9 @@
       <c r="O7" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="Q7" s="3" t="n">
         <v>30.4</v>
       </c>
@@ -1022,25 +1020,25 @@
         <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>142.6</v>
+        <v>42.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>19</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>26.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.9</v>
+        <v>19.2</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>81.8</v>
+        <v>27.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1057,26 +1055,26 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>19.4</v>
+      <c r="H8" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>15.1</v>
+        <v>1.1</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="n">
@@ -1099,12 +1097,12 @@
         <v>19.7</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>45</v>
+        <v>45.9</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="W8" s="3" t="n">
@@ -1137,20 +1135,18 @@
       <c r="E9" s="3" t="n">
         <v>88.7</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>115.2</v>
-      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="n">
-        <v>57.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>26.6</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>18.6</v>
@@ -1159,46 +1155,46 @@
         <v>91.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>42.3</v>
+        <v>423.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>142.8</v>
+        <v>192.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>106</v>
+        <v>186</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>100.8</v>
+        <v>102.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2099.1</v>
+        <v>263.1</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>992.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>12.7</v>
+        <v>127.2</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>11.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>19.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>229.9</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>615</v>
+        <v>68</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1214,20 +1210,20 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="8" t="n">
         <v>29.2</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>11.7</v>
+        <v>17.7</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>13.4</v>
+        <v>23.4</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>11.3</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>6.9</v>
@@ -1236,10 +1232,10 @@
         <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.5</v>
+        <v>51.1</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1251,7 +1247,7 @@
         <v>84.7</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>29.2</v>
@@ -1263,7 +1259,7 @@
         <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
@@ -1278,7 +1274,7 @@
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.9</v>
@@ -1297,23 +1293,23 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="8" t="n">
-        <v>28.4</v>
+      <c r="D11" s="3" t="n">
+        <v>3.5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16.8</v>
+        <v>46.5</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>11.6</v>
+        <v>41.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>5.4</v>
+        <v>54.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1324,20 +1320,20 @@
       <c r="L11" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>1.8</v>
+      <c r="M11" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>890.9</v>
+        <v>82</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q11" s="8" t="n">
-        <v>18.9</v>
+      <c r="Q11" s="3" t="n">
+        <v>28.9</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>20</v>
@@ -1346,7 +1342,7 @@
         <v>18.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1.8</v>
+        <v>47.5</v>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
@@ -1367,11 +1363,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>51.3</v>
-      </c>
+      <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="n">
-        <v>28.2</v>
+        <v>18.4</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>18</v>
@@ -1401,7 +1395,7 @@
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>19.2</v>
+        <v>1.9</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
@@ -1410,16 +1404,16 @@
         <v>2.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="R12" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>31</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="n">
@@ -1428,14 +1422,14 @@
       <c r="W12" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="X12" s="8" t="n">
-        <v>97.09999999999999</v>
+      <c r="X12" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>19.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1450,14 +1444,12 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>3.1</v>
-      </c>
+      <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1.7</v>
+        <v>17.2</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>21.6</v>
@@ -1466,7 +1458,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>41.2</v>
+        <v>17.4</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>6</v>
@@ -1475,22 +1467,22 @@
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>283.5</v>
+        <v>23.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>41.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>26</v>
@@ -1499,15 +1491,15 @@
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>51.1</v>
+        <v>57.1</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V13" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1517,11 +1509,9 @@
         <v>19.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z13" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>764</v>
+      </c>
+      <c r="Z13" s="3" t="inlineStr"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1542,19 +1532,17 @@
       <c r="E14" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
+      <c r="F14" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="n">
-        <v>27.8</v>
+        <v>47.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
@@ -1566,8 +1554,8 @@
       <c r="M14" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>87.8</v>
+      <c r="N14" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>74.5</v>
@@ -1575,32 +1563,32 @@
       <c r="P14" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="Q14" s="8" t="n">
-        <v>86.8</v>
+      <c r="Q14" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>3.4</v>
+        <v>17.4</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>10.6</v>
@@ -1625,8 +1613,8 @@
       <c r="E15" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>23</v>
+      <c r="F15" s="8" t="n">
+        <v>83.8</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11</v>
@@ -1641,8 +1629,8 @@
         <v>10.2</v>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="8" t="n">
-        <v>18.6</v>
+      <c r="L15" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>16.8</v>
@@ -1651,10 +1639,10 @@
         <v>18.1</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>84</v>
+        <v>8.4</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
@@ -1701,11 +1689,9 @@
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="n">
-        <v>1198.8</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>90.90000000000001</v>
-      </c>
+        <v>1038.8</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="3" t="n">
         <v>1113.9</v>
       </c>
@@ -1713,40 +1699,38 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>22</v>
+        <v>3019.1</v>
       </c>
       <c r="I16" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>90.59999999999999</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>900.6</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>980.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>90.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>920</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>118.2</v>
-      </c>
+        <v>5.7</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="3" t="n">
-        <v>2281.2</v>
+        <v>838.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>104.1</v>
+        <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>266.2</v>
@@ -1755,19 +1739,19 @@
         <v>86.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>152.8</v>
+        <v>122.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>94.5</v>
+        <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>92.3</v>
+        <v>93.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>304.8</v>
+        <v>102</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>14.1</v>
+        <v>61</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1782,11 +1766,9 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="n">
-        <v>27.8</v>
+        <v>21.8</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>17.8</v>
@@ -1798,7 +1780,7 @@
         <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>16.8</v>
+        <v>26.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>6.1</v>
@@ -1810,23 +1792,23 @@
       <c r="L17" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>84</v>
+        <v>8.4</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>13.8</v>
@@ -1835,19 +1817,19 @@
         <v>52.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>17.8</v>
+        <v>1.7</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>18.7</v>
+        <v>0.1</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>12.2</v>
@@ -1865,56 +1847,52 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>24.1</v>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H18" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>12.6</v>
+      <c r="J18" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>62.1</v>
+        <v>18.6</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>14.6</v>
+        <v>78.8</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>21.8</v>
+        <v>30.4</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>48.8</v>
@@ -1923,7 +1901,7 @@
         <v>22.2</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>26.4</v>
+        <v>46.4</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.2</v>
@@ -1946,7 +1924,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D19" s="3" t="n">
         <v>29.6</v>
       </c>
@@ -1956,11 +1936,11 @@
       <c r="F19" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G19" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>6.8</v>
@@ -1969,23 +1949,23 @@
         <v>11.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>87</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="P19" s="3" t="inlineStr"/>
       <c r="Q19" s="3" t="n">
-        <v>29.6</v>
+        <v>23.6</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>20.8</v>
@@ -1994,13 +1974,13 @@
         <v>19.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>46.8</v>
+        <v>96.8</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.1</v>
+        <v>26.9</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
@@ -2009,10 +1989,10 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>19.9</v>
+        <v>14.5</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2029,7 +2009,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="n">
-        <v>18.6</v>
+        <v>10.6</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>18.2</v>
@@ -2042,19 +2022,19 @@
         <v>17.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>117.4</v>
+      <c r="M20" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>19</v>
@@ -2078,7 +2058,7 @@
         <v>48.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>26.4</v>
@@ -2090,7 +2070,7 @@
         <v>20</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58</v>
+        <v>58.8</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>14.4</v>
@@ -2110,13 +2090,13 @@
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="n">
-        <v>26.8</v>
+        <v>16.6</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>22.3</v>
+        <v>2.2</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>8.6</v>
@@ -2128,19 +2108,19 @@
         <v>6.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>81</v>
@@ -2156,10 +2136,10 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>26</v>
+        <v>256</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
@@ -2167,11 +2147,11 @@
       <c r="W21" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="X21" s="8" t="n">
-        <v>18.8</v>
+      <c r="X21" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2191,13 +2171,13 @@
       </c>
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="n">
-        <v>29.4</v>
+        <v>28.4</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>10.8</v>
@@ -2236,7 +2216,7 @@
         <v>19</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>19.5</v>
+        <v>1.9</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>68.3</v>
@@ -2244,15 +2224,17 @@
       <c r="U22" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="W22" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="n">
+        <v>155.1</v>
+      </c>
       <c r="Y22" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>5.7</v>
@@ -2270,77 +2252,75 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="n">
-        <v>195.6</v>
+        <v>19.6</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>11.1</v>
+        <v>117.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>26.2</v>
+        <v>25.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>529.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>52.9</v>
+        <v>22.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>88</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>926.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>140.4</v>
+        <v>44</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>103.4</v>
+        <v>103.9</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1180.4</v>
+        <v>100.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>267.9</v>
+        <v>8267.799999999999</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>123.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>20.6</v>
+        <v>25.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>41.8</v>
+        <v>94.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>2216.1</v>
+        <v>205.4</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>24.8</v>
+        <v>22.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2355,23 +2335,21 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C24" s="3" t="inlineStr"/>
       <c r="D24" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>12.1</v>
+      <c r="F24" s="8" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2379,7 +2357,9 @@
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>18.6</v>
       </c>
@@ -2408,7 +2388,7 @@
         <v>53.5</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>24.7</v>
@@ -2417,7 +2397,7 @@
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.9</v>
+        <v>12.9</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>61</v>
@@ -2438,66 +2418,62 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>81.5</v>
-      </c>
+      <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>16.4</v>
+        <v>12.8</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>23</v>
+        <v>2.3</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>20.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>56.9</v>
+        <v>10.8</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>221.8</v>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
       <c r="R25" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>20.9</v>
+        <v>662.3</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="W25" s="8" t="n">
-        <v>86.40000000000001</v>
+        <v>19.8</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="inlineStr"/>
@@ -2516,28 +2492,28 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="E26" s="8" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G26" s="8" t="n">
-        <v>10.2</v>
+      <c r="E26" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2548,11 +2524,9 @@
       <c r="M26" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>48.4</v>
-      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>69.8</v>
+        <v>6</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>3</v>
@@ -2570,10 +2544,10 @@
         <v>12.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>29.4</v>
+        <v>43.8</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>49.4</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>18.6</v>
@@ -2582,10 +2556,10 @@
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>38.5</v>
+        <v>18.6</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>112.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2601,31 +2575,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>27.4</v>
+        <v>12.7</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>22.8</v>
+        <v>12.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>6.9</v>
+        <v>68.7</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
@@ -2633,16 +2607,18 @@
       <c r="M27" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N27" s="8" t="n">
-        <v>21.8</v>
+      <c r="N27" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>188.9</v>
+        <v>22.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="R27" s="3" t="n">
         <v>20.8</v>
       </c>
@@ -2650,7 +2626,7 @@
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>12.8</v>
@@ -2681,12 +2657,14 @@
       </c>
       <c r="C28" s="3" t="inlineStr"/>
       <c r="D28" s="3" t="n">
-        <v>18.4</v>
+        <v>1.5</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F28" s="3" t="inlineStr"/>
+        <v>14.8</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
@@ -2705,25 +2683,25 @@
       <c r="L28" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>17.8</v>
+      <c r="M28" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>5294</v>
+        <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>21.4</v>
+        <v>27.4</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T28" s="3" t="n">
@@ -2758,7 +2736,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="n">
-        <v>26.8</v>
+        <v>6.8</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>17.4</v>
@@ -2803,13 +2781,13 @@
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>659.5</v>
+        <v>1.8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>13.2</v>
+        <v>152.5</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>23.6</v>
@@ -2817,8 +2795,8 @@
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>12.8</v>
+      <c r="X29" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2839,27 +2817,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D30" s="3" t="n">
-        <v>1952.4</v>
+        <v>1334.8</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>80.8</v>
+        <v>85.8</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1816.8</v>
+        <v>109.8</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>47.4</v>
+        <v>48.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2016.1</v>
+        <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2681.4</v>
+        <v>32.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>90.40000000000001</v>
@@ -2868,22 +2848,22 @@
         <v>91.40000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>836.5</v>
+        <v>185.4</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>19</v>
+        <v>904.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>420</v>
+        <v>43464.4</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>132</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1082</v>
+        <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>102.2</v>
@@ -2892,22 +2872,22 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>10</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1818.2</v>
+        <v>118.2</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>985.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>418.1</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>316.2</v>
+        <v>3136.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>49.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2923,7 +2903,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>26.6</v>
@@ -2941,14 +2921,16 @@
         <v>26.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>85.2</v>
+      </c>
       <c r="L31" s="8" t="n">
-        <v>318.3</v>
+        <v>18.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
@@ -2987,7 +2969,7 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>69.2</v>
+        <v>475.1</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>10</v>
@@ -3005,20 +2987,16 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>18.9</v>
+        <v>0.9</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>15.2</v>
@@ -3042,37 +3020,37 @@
         <v>18.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>86.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="R32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R32" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="V32" s="8" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3088,14 +3066,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="n">
-        <v>18.4</v>
+        <v>8.6</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>18</v>
+        <v>1.8</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>23.1</v>
@@ -3107,10 +3083,10 @@
         <v>17.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -3119,21 +3095,21 @@
         <v>17.4</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>15.6</v>
+        <v>1.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>84</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R33" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="R33" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3148,7 +3124,7 @@
       <c r="V33" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3173,15 +3149,15 @@
       </c>
       <c r="C34" s="3" t="inlineStr"/>
       <c r="D34" s="3" t="n">
-        <v>24.2</v>
+        <v>10.8</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="G34" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3206,15 +3182,15 @@
         <v>18.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3226,14 +3202,14 @@
       <c r="U34" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="V34" s="8" t="n">
-        <v>284.6</v>
+      <c r="V34" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="Y34" s="3" t="inlineStr"/>
       <c r="Z34" s="3" t="inlineStr"/>
@@ -3251,7 +3227,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>28.6</v>
@@ -3260,7 +3236,7 @@
         <v>17.8</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>21.8</v>
+        <v>3.2</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>10.8</v>
@@ -3268,8 +3244,8 @@
       <c r="H35" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="I35" s="8" t="n">
-        <v>11</v>
+      <c r="I35" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
@@ -3287,16 +3263,16 @@
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="P35" s="8" t="n">
-        <v>12.9</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>190.8</v>
+        <v>19</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.9</v>
@@ -3310,7 +3286,7 @@
       <c r="V35" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3331,17 +3307,15 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C36" s="3" t="inlineStr"/>
       <c r="D36" s="3" t="n">
-        <v>48.6</v>
+        <v>12.8</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>22.2</v>
+        <v>12.2</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>10.8</v>
@@ -3350,7 +3324,7 @@
         <v>16.8</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>8</v>
@@ -3362,7 +3336,7 @@
         <v>18.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>18.8</v>
@@ -3386,7 +3360,7 @@
         <v>26.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>460.8</v>
+        <v>17</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.4</v>
@@ -3416,73 +3390,73 @@
       </c>
       <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="3" t="n">
-        <v>1120.8</v>
+        <v>1138.8</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>80.2</v>
+        <v>88.2</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>111</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>498.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>808</v>
+        <v>898</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>21816.4</v>
+        <v>210.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>219.8</v>
+        <v>31.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>118.2</v>
+        <v>1.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>11.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1082.2</v>
+        <v>82.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>4920.8</v>
+        <v>12.6</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>14.9</v>
+        <v>44.5</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1102.2</v>
+        <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>101.9</v>
+        <v>10.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>288.6</v>
+        <v>208.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>14.1</v>
+        <v>44.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>109.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>106.8</v>
+        <v>156</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>231.2</v>
+        <v>31.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3517,15 +3491,15 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3544,16 +3518,16 @@
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>28.3</v>
+        <v>88.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>38.7</v>
+        <v>57.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22</v>
+        <v>240.1</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>19</v>
@@ -3578,74 +3552,70 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="3" t="n">
-        <v>26</v>
+        <v>26.6</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>2.6</v>
+        <v>43.6</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>46.8</v>
+        <v>4.8</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>36.1</v>
+        <v>3.8</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>19</v>
+      <c r="M39" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>898.6</v>
+        <v>8.4</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="Q39" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>40.8</v>
-      </c>
+      <c r="R39" s="3" t="inlineStr"/>
       <c r="S39" s="8" t="n">
-        <v>92.8</v>
+        <v>19.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>86.8</v>
+        <v>26</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>29.4</v>
+        <v>23.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>10.6</v>
+        <v>18.6</v>
       </c>
       <c r="X39" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>69.8</v>
+        <v>64.2</v>
       </c>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
@@ -3662,31 +3632,29 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>26.2</v>
+        <v>16.2</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>16.4</v>
+        <v>22.8</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J40" s="3" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.2</v>
@@ -3701,19 +3669,19 @@
         <v>84</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.2</v>
+        <v>16.2</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>91.8</v>
+        <v>51.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>14.4</v>
@@ -3745,10 +3713,10 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>18.4</v>
@@ -3757,28 +3725,28 @@
         <v>21.9</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.5</v>
+        <v>43.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>18.9</v>
+        <v>1.7</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
@@ -3790,12 +3758,14 @@
       <c r="R41" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S41" s="3" t="inlineStr"/>
+      <c r="S41" s="3" t="n">
+        <v>17.2</v>
+      </c>
       <c r="T41" s="3" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v>108.4</v>
+        <v>62.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>19.6</v>
@@ -3804,7 +3774,7 @@
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>76.5</v>
@@ -3825,9 +3795,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C42" s="3" t="inlineStr"/>
       <c r="D42" s="3" t="n">
         <v>30.4</v>
       </c>
@@ -3835,18 +3803,18 @@
         <v>16</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="I42" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
@@ -3857,7 +3825,7 @@
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12</v>
+        <v>17.8</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>85</v>
@@ -3869,7 +3837,7 @@
         <v>28.6</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
       <c r="T42" s="3" t="n">
@@ -3881,17 +3849,17 @@
       <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="8" t="n">
+      <c r="W42" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X42" s="8" t="n">
+      <c r="X42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>57</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3908,22 +3876,20 @@
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="n">
-        <v>30.4</v>
+        <v>10.4</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>22.7</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>17.2</v>
+        <v>19.2</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>15</v>
@@ -3946,25 +3912,25 @@
       <c r="P43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" s="8" t="n">
-        <v>9.4</v>
+      <c r="Q43" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="S43" s="8" t="n">
-        <v>18</v>
+      <c r="S43" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>29.9</v>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="8" t="n">
+      <c r="W43" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -3989,15 +3955,17 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="E44" s="3" t="n">
+      <c r="C44" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>14.2</v>
@@ -4006,17 +3974,19 @@
         <v>15.8</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K44" s="3" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M44" s="8" t="n">
-        <v>26.5</v>
+      <c r="M44" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="N44" s="8" t="n">
         <v>16.4</v>
@@ -4025,7 +3995,7 @@
         <v>80.8</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>30.6</v>
@@ -4039,14 +4009,12 @@
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="8" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U44" s="3" t="inlineStr"/>
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="8" t="n">
-        <v>20.8</v>
+      <c r="W44" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4068,56 +4036,52 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="3" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>288.4</v>
+        <v>830.6</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>92.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>22</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.8</v>
+        <v>61</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1189.6</v>
+        <v>1089.6</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1102.7</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>17992.6</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1662</v>
+        <v>650.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>121</v>
+        <v>1.3</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>11.6</v>
+        <v>746.4</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>217.9</v>
@@ -4126,13 +4090,13 @@
         <v>107.1</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>192.8</v>
+        <v>12.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>112</v>
+        <v>114.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>322.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>64.40000000000001</v>
@@ -4152,23 +4116,23 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="8" t="n">
-        <v>71.90000000000001</v>
+      <c r="D46" s="3" t="n">
+        <v>61.9</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>10.2</v>
@@ -4177,11 +4141,11 @@
       <c r="L46" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>85.40000000000001</v>
+      <c r="M46" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>83.09999999999999</v>
@@ -4190,19 +4154,19 @@
         <v>3.6</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>23</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>18.8</v>
+        <v>17.8</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>23.8</v>
@@ -4214,7 +4178,7 @@
         <v>19.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>119.4</v>
+        <v>165.4</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
@@ -737,19 +737,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>18.2</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>6.8</v>
@@ -761,35 +761,33 @@
         <v>18.6</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>6.8</v>
+        <v>18.8</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>86.8</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="O4" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+      <c r="R4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="T4" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" s="3" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
@@ -808,7 +806,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D5" s="3" t="n">
         <v>28.4</v>
       </c>
@@ -831,21 +831,23 @@
         <v>9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>18.6</v>
+        <v>17.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
+        <v>83.59999999999999</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="Q5" s="3" t="n">
         <v>28.4</v>
       </c>
@@ -856,7 +858,7 @@
         <v>21.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>58</v>
+        <v>54.8</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>16.8</v>
@@ -871,7 +873,7 @@
         <v>17.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>5.6</v>
+        <v>56.5</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>13.6</v>
@@ -889,15 +891,17 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D6" s="3" t="n">
-        <v>2.8</v>
+        <v>28.6</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.5</v>
+        <v>23.9</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10.8</v>
@@ -924,7 +928,7 @@
         <v>18.2</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>86</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>3</v>
@@ -939,13 +943,13 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>58</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>25.8</v>
+        <v>24.6</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>20</v>
@@ -972,14 +976,18 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D7" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>24.1</v>
+      </c>
       <c r="G7" s="3" t="n">
         <v>12.6</v>
       </c>
@@ -990,28 +998,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>7.4</v>
+        <v>89.5</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>30.4</v>
+      <c r="Q7" s="8" t="n">
+        <v>0.4</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>20.6</v>
@@ -1020,25 +1028,25 @@
         <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>42.6</v>
+        <v>656.4</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>0.4</v>
+        <v>25.8</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="X7" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1055,20 +1063,22 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="n">
-        <v>22.9</v>
+        <v>30.6</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>235.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
@@ -1076,9 +1086,11 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="M8" s="3" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>17.4</v>
@@ -1086,7 +1098,9 @@
       <c r="O8" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="Q8" s="3" t="n">
         <v>30.6</v>
       </c>
@@ -1097,23 +1111,25 @@
         <v>19.7</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>45.9</v>
+        <v>42.6</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>26.2</v>
       </c>
       <c r="W8" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>19.4</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="n">
-        <v>14.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1130,23 +1146,25 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="n">
-        <v>142.8</v>
+        <v>148.8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
+        <v>887.1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>17.2</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>27.1</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>18.6</v>
@@ -1158,7 +1176,7 @@
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>423.5</v>
@@ -1167,16 +1185,16 @@
         <v>16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>192.8</v>
+        <v>142.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>186</v>
+        <v>1196</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>102.6</v>
+        <v>182.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>263.1</v>
+        <v>9255.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
@@ -1185,16 +1203,16 @@
         <v>127.2</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>971.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>229.9</v>
+        <v>26.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1210,7 +1228,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="E10" s="3" t="n">
@@ -1220,7 +1238,7 @@
         <v>23.4</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>16.5</v>
@@ -1229,10 +1247,10 @@
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.3</v>
+        <v>1.1</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>51.1</v>
+        <v>0.1</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>18.8</v>
@@ -1256,10 +1274,10 @@
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>20.5</v>
+        <v>90.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
@@ -1274,10 +1292,10 @@
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1293,23 +1311,23 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="n">
-        <v>3.5</v>
+      <c r="D11" s="8" t="n">
+        <v>28.4</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>13.2</v>
+        <v>1.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>54.6</v>
+        <v>15.4</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1327,28 +1345,38 @@
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>28.9</v>
+        <v>28.4</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>18.4</v>
+        <v>13.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr"/>
+        <v>425.4</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>195.1</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>48.9</v>
+      </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1363,15 +1391,17 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D12" s="3" t="n">
-        <v>18.4</v>
+        <v>28.2</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>23.1</v>
+        <v>43.1</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>10.2</v>
@@ -1391,7 +1421,7 @@
       <c r="L12" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1401,7 +1431,7 @@
         <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>2.8</v>
@@ -1413,23 +1443,25 @@
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="U12" s="3" t="inlineStr"/>
+        <v>257.1</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="V12" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>19.8</v>
+        <v>45.4</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>13.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1446,10 +1478,10 @@
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>17.2</v>
+        <v>11.2</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>21.6</v>
@@ -1458,7 +1490,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>6</v>
@@ -1467,7 +1499,7 @@
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>17.6</v>
@@ -1479,10 +1511,10 @@
         <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>23.5</v>
+        <v>83.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>26</v>
@@ -1491,27 +1523,29 @@
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>57.1</v>
+        <v>58</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>19.8</v>
+        <v>22.6</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>764</v>
-      </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>13</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1535,14 +1569,16 @@
       <c r="F14" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="H14" s="3" t="n">
-        <v>47.8</v>
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="8" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
@@ -1554,11 +1590,11 @@
       <c r="M14" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>74.5</v>
+        <v>714.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
@@ -1567,19 +1603,19 @@
         <v>26.8</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58</v>
+        <v>51.5</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>17.4</v>
@@ -1588,7 +1624,7 @@
         <v>16.8</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>10.6</v>
@@ -1613,8 +1649,8 @@
       <c r="E15" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>83.8</v>
+      <c r="F15" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11</v>
@@ -1628,9 +1664,11 @@
       <c r="J15" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="n">
-        <v>11.8</v>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>16.8</v>
@@ -1639,10 +1677,10 @@
         <v>18.1</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>8.4</v>
+        <v>84</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>13.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
@@ -1657,22 +1695,22 @@
         <v>52.1</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>17</v>
+        <v>18.8</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>114.6</v>
+        <v>17.8</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1687,44 +1725,50 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D16" s="3" t="n">
-        <v>1038.8</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
+        <v>138.8</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>89</v>
+      </c>
       <c r="F16" s="3" t="n">
-        <v>1113.9</v>
+        <v>113.9</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3019.1</v>
+        <v>288.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>909.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="P16" s="3" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>118.2</v>
+      </c>
       <c r="Q16" s="3" t="n">
-        <v>838.2</v>
+        <v>138.2</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>102.1</v>
@@ -1733,7 +1777,7 @@
         <v>98.8</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>266.2</v>
+        <v>66.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>86.2</v>
@@ -1745,13 +1789,13 @@
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>102</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1768,7 +1812,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>17.8</v>
@@ -1777,10 +1821,10 @@
         <v>22.8</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>26.8</v>
+        <v>16.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>6.1</v>
@@ -1795,26 +1839,26 @@
       <c r="M17" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>18.1</v>
+      <c r="N17" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>27.6</v>
+        <v>2.7</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>20.4</v>
+        <v>11.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>13.8</v>
+        <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>52.2</v>
+        <v>51.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>1.7</v>
@@ -1823,16 +1867,16 @@
         <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0.1</v>
+        <v>15.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>60.4</v>
+        <v>1068.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>12.2</v>
+        <v>810.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1847,70 +1891,78 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
+        <v>30.4</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>44.5</v>
+      </c>
       <c r="F18" s="3" t="n">
-        <v>8.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.1</v>
+        <v>13.6</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>13.6</v>
+        <v>456.1</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>13.6</v>
+        <v>126.1</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>18.6</v>
+        <v>49.6</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>17.8</v>
+        <v>4.7</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>78.8</v>
+        <v>138.8</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="R18" s="8" t="n">
-        <v>29.8</v>
+        <v>904.7</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44.8</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>48.8</v>
+        <v>457.1</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>22.2</v>
+        <v>4.4</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>46.4</v>
+        <v>464.7</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>20.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y18" s="3" t="inlineStr"/>
-      <c r="Z18" s="3" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>38</v>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1924,9 +1976,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="n">
         <v>29.6</v>
       </c>
@@ -1934,13 +1984,13 @@
         <v>17.8</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>6.8</v>
@@ -1949,7 +1999,7 @@
         <v>11.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.6</v>
@@ -1957,15 +2007,17 @@
       <c r="M19" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>18.7</v>
+      <c r="N19" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="n">
-        <v>23.6</v>
+        <v>81</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>20.8</v>
@@ -1974,7 +2026,7 @@
         <v>19.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>96.8</v>
+        <v>46.8</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>22</v>
@@ -1989,10 +2041,10 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>24</v>
+        <v>294</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2007,7 +2059,9 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D20" s="3" t="n">
         <v>10.6</v>
       </c>
@@ -2017,12 +2071,14 @@
       <c r="F20" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
+      <c r="G20" s="8" t="n">
+        <v>12.4</v>
+      </c>
       <c r="H20" s="8" t="n">
-        <v>17.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>12.6</v>
@@ -2055,10 +2111,10 @@
         <v>20.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>48.8</v>
+        <v>47.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>26.4</v>
@@ -2070,10 +2126,10 @@
         <v>20</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58.8</v>
+        <v>58</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2090,7 +2146,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="n">
-        <v>16.6</v>
+        <v>26.6</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
@@ -2108,19 +2164,19 @@
         <v>6.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>1.8</v>
+        <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>81</v>
@@ -2128,7 +2184,9 @@
       <c r="P21" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="n">
+        <v>26.6</v>
+      </c>
       <c r="R21" s="3" t="n">
         <v>20</v>
       </c>
@@ -2136,22 +2194,22 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>256</v>
+        <v>56.8</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2169,15 +2227,17 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D22" s="3" t="n">
         <v>28.4</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.7</v>
+        <v>17.6</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>10.8</v>
@@ -2195,13 +2255,13 @@
         <v>6.8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>87</v>
@@ -2213,10 +2273,10 @@
         <v>23.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>68.3</v>
@@ -2224,20 +2284,20 @@
       <c r="U22" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>155.1</v>
+        <v>445.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.7</v>
+        <v>254.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2252,75 +2312,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D23" s="3" t="n">
-        <v>19.6</v>
+        <v>14.5</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>117.8</v>
+        <v>17.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>25.2</v>
+        <v>36.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>529.5</v>
+        <v>311.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>22.9</v>
+        <v>52.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>26.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>12.8</v>
+        <v>15.6</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>44</v>
+        <v>140.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>103.9</v>
+        <v>103.4</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>100.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>8267.799999999999</v>
+        <v>468</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>123.5</v>
+        <v>1123.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>25.6</v>
+        <v>935.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>94.8</v>
+        <v>26</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>205.4</v>
+        <v>7050.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>22.8</v>
+        <v>652.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2342,14 +2404,14 @@
       <c r="E24" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>37.5</v>
+      <c r="F24" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2357,9 +2419,7 @@
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>18.6</v>
       </c>
@@ -2367,16 +2427,16 @@
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>18.4</v>
+        <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q24" s="3" t="n">
-        <v>28.1</v>
+      <c r="Q24" s="8" t="n">
+        <v>84.09999999999999</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>20.7</v>
@@ -2385,25 +2445,25 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>53.5</v>
+        <v>0.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>24.7</v>
+        <v>1.8</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>11.1</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>19.1</v>
+        <v>10.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>12.9</v>
+        <v>10</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>61</v>
+        <v>118.9</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.6</v>
+        <v>1.2</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2418,21 +2478,21 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>1.6</v>
-      </c>
+        <v>22.8</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>2.3</v>
+        <v>19.4</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11.6</v>
+        <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.6</v>
+        <v>1.2</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2444,40 +2504,48 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>83.5</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q25" s="3" t="inlineStr"/>
+        <v>5.4</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>91.40000000000001</v>
+      </c>
       <c r="R25" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>662.3</v>
+        <v>405.5</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>12.8</v>
+        <v>156.1</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X25" s="3" t="inlineStr"/>
-      <c r="Y25" s="3" t="inlineStr"/>
-      <c r="Z25" s="3" t="inlineStr"/>
+        <v>7.8</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2491,29 +2559,27 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="C26" s="3" t="inlineStr"/>
       <c r="D26" s="3" t="n">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1.7</v>
+        <v>17.2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2.2</v>
+        <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>16</v>
+        <v>11.6</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.1</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2524,12 +2590,14 @@
       <c r="M26" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
@@ -2541,13 +2609,13 @@
         <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>12.2</v>
+        <v>52.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v>49.4</v>
+        <v>18.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>24.4</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>18.6</v>
@@ -2556,10 +2624,10 @@
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>18.6</v>
+        <v>28.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>19.8</v>
+        <v>112.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2574,50 +2642,48 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>12.7</v>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="8" t="n">
+        <v>27.4</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>7.2</v>
+        <v>15.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>12.8</v>
+        <v>22.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>16.8</v>
+        <v>11</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>68.7</v>
+        <v>6.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>18.1</v>
+        <v>10.6</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.4</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4.1</v>
+        <v>21.4</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>20.8</v>
@@ -2626,13 +2692,13 @@
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>12.8</v>
+        <v>15.8</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>24.8</v>
+        <v>64.8</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>19.8</v>
@@ -2640,8 +2706,12 @@
       <c r="X27" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="Y27" s="3" t="inlineStr"/>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2655,42 +2725,44 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D28" s="3" t="n">
-        <v>1.5</v>
+        <v>27.4</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>14.8</v>
+        <v>18.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.7</v>
+        <v>22.8</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>16</v>
+      <c r="H28" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>18.1</v>
       </c>
       <c r="L28" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.6</v>
+        <v>16.6</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>10.7</v>
+        <v>17.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>3.4</v>
@@ -2705,22 +2777,26 @@
         <v>20.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>56.7</v>
+        <v>56.9</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>25.6</v>
+        <v>29.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>19.8</v>
+        <v>17.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y28" s="3" t="inlineStr"/>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2734,12 +2810,14 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D29" s="3" t="n">
-        <v>6.8</v>
+        <v>26.8</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>17.4</v>
+        <v>15.9</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>22.1</v>
@@ -2747,17 +2825,17 @@
       <c r="G29" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>18.6</v>
@@ -2781,13 +2859,13 @@
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>1.8</v>
+        <v>59.8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>152.5</v>
+        <v>13.2</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>23.6</v>
@@ -2795,8 +2873,8 @@
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>19.8</v>
+      <c r="X29" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2817,44 +2895,42 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="n">
-        <v>1334.8</v>
+        <v>133.2</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>109.8</v>
+        <v>9.5</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>48.4</v>
+        <v>474.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>32.8</v>
+        <v>39.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>308.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>9434.799999999999</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>185.4</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>904.6</v>
+        <v>90.2</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>43464.4</v>
+        <v>681.1</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>15.2</v>
@@ -2872,22 +2948,22 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>118.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>418.1</v>
+        <v>0.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>3136.2</v>
+        <v>916.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.6</v>
+        <v>47.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2903,7 +2979,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>26.6</v>
@@ -2915,10 +2991,10 @@
         <v>21.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>26.1</v>
+        <v>1.6</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>4</v>
@@ -2926,20 +3002,18 @@
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="L31" s="8" t="n">
-        <v>18.3</v>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n">
+        <v>10.2</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>18</v>
+        <v>10.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>205.1</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>3</v>
@@ -2948,7 +3022,7 @@
         <v>26.4</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>20.4</v>
+        <v>10.4</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>20.4</v>
@@ -2957,7 +3031,7 @@
         <v>59.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>19.2</v>
+        <v>1.4</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>23.6</v>
@@ -2969,10 +3043,10 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>475.1</v>
+        <v>17.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2989,9 +3063,11 @@
       </c>
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E32" s="3" t="inlineStr"/>
+        <v>26.2</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>13.6</v>
+      </c>
       <c r="F32" s="3" t="n">
         <v>21.9</v>
       </c>
@@ -2999,16 +3075,16 @@
         <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>15.2</v>
+        <v>0.1</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>11.8</v>
+        <v>2</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>18.4</v>
@@ -3016,43 +3092,39 @@
       <c r="M32" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>3</v>
-      </c>
+        <v>4.8</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R32" s="8" t="n">
-        <v>19.8</v>
+        <v>2.4</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>22.6</v>
-      </c>
+        <v>96.8</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="V32" s="3" t="inlineStr"/>
       <c r="W32" s="3" t="n">
-        <v>18.8</v>
+        <v>449.1</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>19.8</v>
+        <v>4412.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>81.8</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>14.6</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3068,13 +3140,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="n">
-        <v>8.6</v>
+        <v>26.6</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1.8</v>
+        <v>17.2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>23.1</v>
+        <v>21.9</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>9.4</v>
@@ -3086,7 +3158,7 @@
         <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -3094,11 +3166,11 @@
       <c r="L33" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>1.5</v>
+      <c r="M33" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>84</v>
@@ -3107,24 +3179,24 @@
         <v>3.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>14.4</v>
+        <v>26.6</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56</v>
+        <v>256</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>15.3</v>
+        <v>1.2</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3133,7 +3205,9 @@
       <c r="Y33" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="n">
+        <v>5.6</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3149,16 +3223,16 @@
       </c>
       <c r="C34" s="3" t="inlineStr"/>
       <c r="D34" s="3" t="n">
-        <v>10.8</v>
+        <v>48.2</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>20.9</v>
+        <v>23.1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>16.6</v>
+        <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>17</v>
@@ -3170,7 +3244,7 @@
         <v>7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="L34" s="8" t="n">
         <v>18.4</v>
@@ -3182,7 +3256,7 @@
         <v>18.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
@@ -3200,7 +3274,7 @@
         <v>57.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>24.6</v>
@@ -3211,8 +3285,12 @@
       <c r="X34" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="Y34" s="3" t="inlineStr"/>
-      <c r="Z34" s="3" t="inlineStr"/>
+      <c r="Y34" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3226,20 +3304,18 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="3" t="n">
-        <v>28.6</v>
+        <v>24.2</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>28.9</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10.8</v>
+        <v>6.6</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>16.8</v>
@@ -3253,32 +3329,32 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
-        <v>17.6</v>
+      <c r="L35" s="8" t="n">
+        <v>17.9</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R35" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R35" s="3" t="n">
         <v>19</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>62.2</v>
+        <v>82.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.4</v>
@@ -3286,14 +3362,18 @@
       <c r="V35" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="Y35" s="3" t="inlineStr"/>
-      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3309,13 +3389,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr"/>
       <c r="D36" s="3" t="n">
-        <v>12.8</v>
+        <v>28.6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.8</v>
+        <v>17.8</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>12.2</v>
+        <v>23.2</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>10.8</v>
@@ -3333,10 +3413,10 @@
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>18.6</v>
+        <v>11.8</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>7.2</v>
+        <v>17.2</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>18.8</v>
@@ -3350,17 +3430,17 @@
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>26.4</v>
+        <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17</v>
+        <v>1.3</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.4</v>
@@ -3372,7 +3452,7 @@
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.5</v>
+        <v>86.8</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3390,70 +3470,70 @@
       </c>
       <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="3" t="n">
-        <v>1138.8</v>
+        <v>120.8</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>88.2</v>
+        <v>8821.799999999999</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>498.6</v>
+        <v>45.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>898</v>
+        <v>87</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>210.9</v>
+        <v>40.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1.6</v>
+        <v>117.2</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>82.2</v>
+        <v>0.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>12.6</v>
+        <v>20.8</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>44.5</v>
+        <v>149.4</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>132.8</v>
+        <v>131.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>102.2</v>
+        <v>1082.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>10.1</v>
+        <v>1181.5</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>208.6</v>
+        <v>288.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>44.7</v>
+        <v>79.8</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>109.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>18.4</v>
+        <v>998.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>10.1</v>
+        <v>101.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3482,7 +3562,7 @@
         <v>22.2</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>17</v>
@@ -3491,19 +3571,17 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
+        <v>6.9</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>17.9</v>
+        <v>1.8</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>86.09999999999999</v>
@@ -3518,27 +3596,29 @@
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>88.5</v>
+        <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>57.7</v>
+        <v>5.4</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>240.1</v>
+        <v>22</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>20.3</v>
+        <v>12790.1</v>
+      </c>
+      <c r="X38" s="8" t="n">
+        <v>111.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3552,61 +3632,63 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="D39" s="3" t="n">
-        <v>26.6</v>
+        <v>463</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>43.6</v>
+        <v>18.6</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>4.6</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
         <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L39" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L39" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>8.4</v>
+        <v>84.8</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R39" s="3" t="inlineStr"/>
-      <c r="S39" s="8" t="n">
+        <v>466.5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>204.8</v>
+      </c>
+      <c r="S39" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>15.8</v>
+        <v>16.5</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>23.9</v>
+        <v>754.3</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>18.6</v>
@@ -3615,9 +3697,11 @@
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="Z39" s="3" t="inlineStr"/>
+        <v>64.8</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>48.8</v>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3631,30 +3715,30 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C40" s="3" t="inlineStr"/>
       <c r="D40" s="3" t="n">
-        <v>16.2</v>
+        <v>26.2</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>8.4</v>
+        <v>16.4</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="8" t="n">
-        <v>8</v>
+      <c r="J40" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.2</v>
@@ -3662,29 +3746,29 @@
       <c r="M40" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="N40" s="8" t="n">
+      <c r="N40" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>84</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>14.4</v>
+        <v>57.8</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20.8</v>
@@ -3713,25 +3797,25 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.1</v>
+        <v>11.1</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>18.4</v>
+        <v>20.4</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>84.90000000000001</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>21.9</v>
+        <v>2.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>17</v>
+        <v>20.1</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>43.5</v>
+        <v>3.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3743,45 +3827,45 @@
         <v>19.4</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>1.7</v>
+        <v>15.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="P41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q41" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.5</v>
+        <v>62.9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>19.6</v>
+        <v>11.2</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3796,36 +3880,38 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="n">
-        <v>30.4</v>
+      <c r="D42" s="8" t="n">
+        <v>48.6</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>14</v>
+      <c r="F42" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>94</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr"/>
+        <v>65.40000000000001</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M42" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M42" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>17.8</v>
+        <v>17</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>85</v>
@@ -3837,9 +3923,11 @@
         <v>28.6</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S42" s="3" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>20.4</v>
+      </c>
       <c r="T42" s="3" t="n">
         <v>52</v>
       </c>
@@ -3856,10 +3944,10 @@
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>57</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3876,17 +3964,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="8" t="n">
-        <v>18.5</v>
+        <v>20.4</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>19.2</v>
+        <v>174.4</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>8.6</v>
@@ -3897,17 +3987,17 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>3</v>
@@ -3916,16 +4006,16 @@
         <v>20.4</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>18.8</v>
+        <v>20.6</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>22.9</v>
+        <v>25.9</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>26.4</v>
@@ -3937,10 +4027,10 @@
         <v>19.6</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>57</v>
+        <v>14.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3956,28 +4046,28 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="E44" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>217</v>
+        <v>12</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>14.2</v>
+        <v>26.1</v>
       </c>
       <c r="H44" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
         <v>15.8</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>1.5</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
@@ -3988,19 +4078,19 @@
       <c r="M44" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>80.8</v>
+        <v>154.8</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R44" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="R44" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4009,12 +4099,14 @@
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="n">
+        <v>2.3</v>
+      </c>
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>30</v>
+        <v>20.6</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4022,7 +4114,9 @@
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="Z44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4038,70 +4132,74 @@
       </c>
       <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="3" t="n">
-        <v>1.8</v>
+        <v>1165.8</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>22.1</v>
+        <v>102.8</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>830.6</v>
+        <v>135.9</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>22</v>
+        <v>53.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61</v>
+        <v>61.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>9.9</v>
+        <v>59.4</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1089.6</v>
+        <v>109.6</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O45" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>499</v>
+      </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>650.2</v>
+        <v>16.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1.3</v>
+        <v>1191.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>746.4</v>
+        <v>115.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>217.9</v>
+        <v>517.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>107.1</v>
+        <v>187.1</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>12.8</v>
+        <v>1543</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>114.8</v>
+        <v>111.5</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.8</v>
+        <v>392.9</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr"/>
+        <v>69.40000000000001</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>11141.1</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4117,16 +4215,16 @@
       </c>
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="3" t="n">
-        <v>61.9</v>
+        <v>27.9</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
+        <v>19.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4137,21 +4235,23 @@
       <c r="J46" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>72162.8</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="N46" s="3" t="n">
-        <v>17.2</v>
+      <c r="N46" s="8" t="n">
+        <v>54.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>3.6</v>
+        <v>17.8</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>27.5</v>
@@ -4159,11 +4259,11 @@
       <c r="R46" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>19.3</v>
+      <c r="S46" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>17.8</v>
@@ -4175,12 +4275,14 @@
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>19.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="Z46" s="3" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -737,16 +728,16 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="3" t="n">
         <v>23</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>18.2</v>
@@ -761,16 +752,16 @@
         <v>18.6</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M4" s="8" t="n">
-        <v>86.8</v>
+        <v>18.6</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>3.4</v>
@@ -807,7 +798,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>28.4</v>
@@ -834,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>15.8</v>
@@ -843,7 +834,7 @@
         <v>16.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>3.4</v>
@@ -901,7 +892,7 @@
         <v>17.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10.8</v>
@@ -928,7 +919,7 @@
         <v>18.2</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>3</v>
@@ -943,7 +934,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -977,7 +968,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>30.4</v>
@@ -995,7 +986,7 @@
         <v>15.6</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>14.4</v>
@@ -1003,10 +994,10 @@
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="M7" s="8" t="n">
+      <c r="L7" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1018,8 +1009,8 @@
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="8" t="n">
-        <v>0.4</v>
+      <c r="Q7" s="3" t="n">
+        <v>30.4</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>20.6</v>
@@ -1028,7 +1019,7 @@
         <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>656.4</v>
+        <v>56.4</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>17</v>
@@ -1039,11 +1030,11 @@
       <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>27.8</v>
+        <v>57.8</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>14</v>
@@ -1068,14 +1059,14 @@
       <c r="E8" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>235.9</v>
+      <c r="F8" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>6.9</v>
@@ -1087,10 +1078,10 @@
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>17.4</v>
+        <v>16.4</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>17.4</v>
@@ -1116,17 +1107,17 @@
       <c r="U8" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>2.4</v>
+        <v>24.2</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>19.4</v>
@@ -1146,7 +1137,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="n">
-        <v>148.8</v>
+        <v>145.8</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>887.1</v>
@@ -1155,16 +1146,16 @@
         <v>17.2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>27.1</v>
+        <v>57.1</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>36.4</v>
+        <v>56.4</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>18.6</v>
@@ -1185,31 +1176,31 @@
         <v>16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>142.8</v>
+        <v>145.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1196</v>
+        <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>182.6</v>
+        <v>122.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>9255.1</v>
+        <v>255.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>127.2</v>
+        <v>12.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>971.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>26.2</v>
+        <v>56.2</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>67</v>
@@ -1247,13 +1238,13 @@
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.1</v>
+        <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1274,10 +1265,10 @@
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>90.5</v>
+        <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
@@ -1292,7 +1283,7 @@
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.4</v>
@@ -1311,7 +1302,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="3" t="n">
         <v>28.4</v>
       </c>
       <c r="E11" s="3" t="n">
@@ -1327,7 +1318,7 @@
         <v>1.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1335,11 +1326,11 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="L11" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M11" s="8" t="n">
-        <v>18.2</v>
+      <c r="M11" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
@@ -1363,7 +1354,7 @@
         <v>425.4</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>2</v>
+        <v>20.2</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>45.4</v>
@@ -1375,7 +1366,7 @@
         <v>9.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>48.9</v>
+        <v>58.9</v>
       </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1401,7 +1392,7 @@
         <v>18</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>43.1</v>
+        <v>23.1</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>10.2</v>
@@ -1421,20 +1412,20 @@
       <c r="L12" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>1.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2.8</v>
+        <v>28.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>21.6</v>
@@ -1443,10 +1434,10 @@
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>257.1</v>
+        <v>57.1</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>45.4</v>
@@ -1481,7 +1472,7 @@
         <v>26</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11.2</v>
+        <v>17.2</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>21.6</v>
@@ -1514,7 +1505,7 @@
         <v>83.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>26</v>
@@ -1567,7 +1558,7 @@
         <v>19.2</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1578,7 +1569,7 @@
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
@@ -1587,14 +1578,14 @@
       <c r="L14" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>714.5</v>
+        <v>74.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
@@ -1605,7 +1596,7 @@
       <c r="R14" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
@@ -1667,7 +1658,7 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="8" t="n">
+      <c r="L15" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="M15" s="3" t="n">
@@ -1741,7 +1732,7 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>288.2</v>
+        <v>81.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
@@ -1753,19 +1744,19 @@
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>909.4</v>
+        <v>904.4</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>40</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>118.2</v>
+        <v>17.2</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>138.2</v>
@@ -1774,7 +1765,7 @@
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>98.8</v>
+        <v>988.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>66.8</v>
@@ -1792,10 +1783,10 @@
         <v>95.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1820,7 +1811,7 @@
       <c r="F17" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1839,44 +1830,44 @@
       <c r="M17" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>19.1</v>
+      <c r="N17" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>2.7</v>
+        <v>27.6</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>11.4</v>
+        <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>51.2</v>
+        <v>53.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>1.7</v>
+        <v>17.2</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1068.5</v>
+        <v>22.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>810.8</v>
+        <v>254.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1955,13 +1946,13 @@
         <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>86</v>
+        <v>14.4</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0.7</v>
+        <v>20.1</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1984,7 +1975,7 @@
         <v>17.8</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>11.8</v>
@@ -2007,17 +1998,17 @@
       <c r="M19" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="N19" s="8" t="n">
-        <v>18.1</v>
+      <c r="N19" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="8" t="n">
-        <v>92.59999999999999</v>
+      <c r="Q19" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>20.8</v>
@@ -2032,7 +2023,7 @@
         <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
@@ -2041,7 +2032,7 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>294</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16</v>
@@ -2063,7 +2054,7 @@
         <v>0.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>10.6</v>
+        <v>30.6</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>18.2</v>
@@ -2071,11 +2062,11 @@
       <c r="F20" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>87.40000000000001</v>
+      <c r="H20" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>7.9</v>
@@ -2084,7 +2075,7 @@
         <v>12.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
@@ -2096,7 +2087,7 @@
         <v>19</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.8</v>
@@ -2129,7 +2120,7 @@
         <v>58</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2152,7 +2143,7 @@
         <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2.2</v>
+        <v>22.3</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>8.6</v>
@@ -2167,7 +2158,7 @@
         <v>2.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
@@ -2176,16 +2167,16 @@
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>20</v>
@@ -2194,10 +2185,10 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
@@ -2209,7 +2200,7 @@
         <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2228,7 +2219,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>28.4</v>
@@ -2255,13 +2246,13 @@
         <v>6.8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>87</v>
@@ -2273,7 +2264,7 @@
         <v>23.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>19.5</v>
@@ -2294,10 +2285,10 @@
         <v>445.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>254.9</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2316,16 +2307,16 @@
         <v>1.1</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>14.5</v>
+        <v>145.6</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>36.2</v>
+        <v>56.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
@@ -2340,10 +2331,10 @@
         <v>6.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>92</v>
@@ -2367,13 +2358,13 @@
         <v>468</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1123.5</v>
+        <v>123.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>935.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>26</v>
@@ -2382,7 +2373,7 @@
         <v>7050.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>652.8</v>
+        <v>62.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2411,7 +2402,7 @@
         <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2430,13 +2421,13 @@
         <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>5.4</v>
+        <v>25.4</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q24" s="8" t="n">
-        <v>84.09999999999999</v>
+      <c r="Q24" s="3" t="n">
+        <v>28.1</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>20.7</v>
@@ -2445,25 +2436,25 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>11.1</v>
+        <v>18.3</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>11.7</v>
       </c>
       <c r="W24" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X24" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="Y24" s="3" t="n">
-        <v>118.9</v>
+        <v>18.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>1.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2486,13 +2477,13 @@
       </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1.2</v>
+        <v>12</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2504,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>7.6</v>
+        <v>17.6</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>16.3</v>
@@ -2541,7 +2532,7 @@
         <v>9.5</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>88.8</v>
+        <v>88</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
@@ -2567,19 +2558,19 @@
         <v>17.2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>23.9</v>
+        <v>23</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <v>16.8</v>
+      <c r="H26" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>8</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2591,13 +2582,13 @@
         <v>16.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
@@ -2624,10 +2615,10 @@
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>28.8</v>
+        <v>58.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>112.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2642,12 +2633,14 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="8" t="n">
+      <c r="C27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>27.4</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>22.8</v>
@@ -2656,7 +2649,7 @@
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11</v>
+        <v>16.2</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
@@ -2665,7 +2658,7 @@
         <v>6.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
@@ -2674,16 +2667,16 @@
         <v>16.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>11.8</v>
+        <v>18.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>21.4</v>
+        <v>27.4</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>20.8</v>
@@ -2692,13 +2685,13 @@
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>64.8</v>
+        <v>24.8</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>19.8</v>
@@ -2732,27 +2725,27 @@
         <v>27.4</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="8" t="n">
-        <v>66</v>
+      <c r="H28" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>8.9</v>
+        <v>2.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="L28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M28" s="3" t="n">
@@ -2777,25 +2770,25 @@
         <v>20.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>56.9</v>
+        <v>56.7</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>29.6</v>
+        <v>25.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>17.8</v>
+        <v>19.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59.9</v>
+        <v>59.2</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2817,7 +2810,7 @@
         <v>26.8</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>15.9</v>
+        <v>17.4</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>22.1</v>
@@ -2825,17 +2818,17 @@
       <c r="G29" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>18.6</v>
@@ -2862,7 +2855,7 @@
         <v>19.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>59.8</v>
+        <v>59.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>13.2</v>
@@ -2873,8 +2866,8 @@
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>19</v>
+      <c r="X29" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2909,13 +2902,13 @@
         <v>474.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>39.8</v>
+        <v>33</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>308.4</v>
@@ -2948,19 +2941,19 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>10.8</v>
+        <v>70.8</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>71.59999999999999</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>916.2</v>
+        <v>336.2</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>47.6</v>
@@ -2994,7 +2987,7 @@
         <v>9.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1.6</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>4</v>
@@ -3004,16 +2997,16 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>205.1</v>
+        <v>5.1</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>3</v>
@@ -3022,7 +3015,7 @@
         <v>26.4</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>10.4</v>
+        <v>20.4</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>20.4</v>
@@ -3046,7 +3039,7 @@
         <v>17.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3084,7 +3077,7 @@
         <v>6.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>18.4</v>
@@ -3094,7 +3087,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>4.8</v>
+        <v>29.8</v>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="n">
@@ -3104,10 +3097,10 @@
         <v>7.4</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1.9</v>
+        <v>19.3</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>96.8</v>
+        <v>56.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>198.1</v>
@@ -3117,10 +3110,10 @@
         <v>449.1</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>4412.8</v>
+        <v>912.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>81.8</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>14.6</v>
@@ -3158,7 +3151,7 @@
         <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -3166,8 +3159,8 @@
       <c r="L33" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <v>19.6</v>
+      <c r="M33" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>16.7</v>
@@ -3185,13 +3178,13 @@
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>256</v>
+        <v>56</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>1.2</v>
+        <v>15.3</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21.8</v>
@@ -3206,7 +3199,7 @@
         <v>75</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3223,10 +3216,10 @@
       </c>
       <c r="C34" s="3" t="inlineStr"/>
       <c r="D34" s="3" t="n">
-        <v>48.2</v>
+        <v>28.2</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>23.1</v>
@@ -3244,9 +3237,9 @@
         <v>7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L34" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3274,7 +3267,7 @@
         <v>57.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>24.6</v>
@@ -3289,7 +3282,7 @@
         <v>67</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3309,10 +3302,10 @@
         <v>24.2</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>28.9</v>
+        <v>17.6</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>6.6</v>
@@ -3321,7 +3314,7 @@
         <v>16.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
@@ -3329,8 +3322,8 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
-        <v>17.9</v>
+      <c r="L35" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.8</v>
@@ -3339,7 +3332,7 @@
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.4</v>
@@ -3354,7 +3347,7 @@
         <v>18.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>82.2</v>
+        <v>62.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.4</v>
@@ -3362,7 +3355,7 @@
       <c r="V35" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3372,7 +3365,7 @@
         <v>86.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>11.8</v>
+        <v>18.6</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>17.2</v>
@@ -3430,7 +3423,7 @@
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3440,7 +3433,7 @@
         <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.3</v>
+        <v>17</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.4</v>
@@ -3452,7 +3445,7 @@
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3468,12 +3461,14 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D37" s="3" t="n">
-        <v>120.8</v>
+        <v>132.8</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>8821.799999999999</v>
+        <v>882.1</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>11</v>
@@ -3491,7 +3486,7 @@
         <v>31.5</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>117.2</v>
+        <v>17.2</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>90.40000000000001</v>
@@ -3503,19 +3498,19 @@
         <v>0.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>20.8</v>
+        <v>30.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>149.4</v>
+        <v>14.4</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>131.8</v>
+        <v>133.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1082.2</v>
+        <v>162.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1181.5</v>
+        <v>101.7</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>288.6</v>
@@ -3527,13 +3522,13 @@
         <v>109.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>998.1</v>
+        <v>250.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>101.4</v>
+        <v>14.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3565,23 +3560,23 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>17</v>
+        <v>1.7</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.8</v>
+        <v>17.9</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>86.09999999999999</v>
@@ -3599,7 +3594,7 @@
         <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>5.4</v>
+        <v>0.1</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
@@ -3608,16 +3603,16 @@
         <v>22</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>12790.1</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>111.9</v>
+        <v>11.1</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>1.4</v>
+        <v>11.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3633,7 +3628,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>463</v>
@@ -3655,7 +3650,7 @@
         <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19.4</v>
@@ -3667,7 +3662,7 @@
         <v>19</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>84.8</v>
+        <v>84</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>9.6</v>
@@ -3679,10 +3674,10 @@
         <v>204.8</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>16.5</v>
@@ -3693,11 +3688,11 @@
       <c r="W39" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64.8</v>
+        <v>64.5</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>48.8</v>
@@ -3720,13 +3715,13 @@
         <v>26.2</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.8</v>
+        <v>7.8</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>16.4</v>
@@ -3735,10 +3730,10 @@
         <v>2.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.4</v>
+        <v>5.4</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.2</v>
@@ -3756,10 +3751,10 @@
         <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>16.2</v>
+        <v>26.2</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
@@ -3767,8 +3762,8 @@
       <c r="T40" s="3" t="n">
         <v>57.8</v>
       </c>
-      <c r="U40" s="8" t="n">
-        <v>94.40000000000001</v>
+      <c r="U40" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20.8</v>
@@ -3797,16 +3792,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>84.90000000000001</v>
+        <v>25.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2.1</v>
+        <v>21.9</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>20.1</v>
@@ -3827,43 +3822,43 @@
         <v>19.4</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1.8</v>
+        <v>18.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.9</v>
+        <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>11.2</v>
+        <v>1.9</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76</v>
+        <v>76.5</v>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
@@ -3880,23 +3875,23 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="8" t="n">
-        <v>48.6</v>
+      <c r="D42" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>94</v>
+      <c r="F42" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>11.6</v>
@@ -3907,7 +3902,7 @@
       <c r="L42" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -3944,10 +3939,10 @@
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>1.4</v>
+        <v>14.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>1.4</v>
+        <v>57</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3964,19 +3959,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>50.1</v>
+        <v>30.4</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>12.1</v>
+        <v>22.7</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>174.4</v>
+        <v>15.4</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>8.6</v>
@@ -3987,17 +3982,17 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="8" t="n">
+      <c r="L43" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M43" s="8" t="n">
+      <c r="M43" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>3</v>
@@ -4008,14 +4003,14 @@
       <c r="R43" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="S43" s="8" t="n">
-        <v>18</v>
+      <c r="S43" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>26.4</v>
@@ -4030,7 +4025,7 @@
         <v>14.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>21.9</v>
+        <v>57</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4054,20 +4049,20 @@
       <c r="E44" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="F44" s="8" t="n">
-        <v>12</v>
+      <c r="F44" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>26.1</v>
+        <v>14.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
@@ -4076,21 +4071,21 @@
         <v>18.8</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>154.8</v>
+        <v>82</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="R44" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="R44" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4100,13 +4095,13 @@
         <v>47</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>2.3</v>
+        <v>23.2</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4115,7 +4110,7 @@
         <v>14.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>21</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4130,15 +4125,17 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D45" s="3" t="n">
-        <v>1165.8</v>
+        <v>167.8</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>102.8</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>135.9</v>
+        <v>135.3</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>65</v>
@@ -4147,13 +4144,13 @@
         <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>53.5</v>
+        <v>33.5</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>61.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>59.4</v>
+        <v>9.4</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>109.6</v>
@@ -4162,10 +4159,10 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>499</v>
+        <v>99</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
@@ -4174,31 +4171,31 @@
         <v>16.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1191.1</v>
+        <v>121</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>115.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>517.9</v>
+        <v>17.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>187.1</v>
+        <v>107.1</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>1543</v>
+        <v>143</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>111.5</v>
+        <v>115</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>392.9</v>
+        <v>93.5</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>11141.1</v>
+        <v>114</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4224,7 +4221,7 @@
         <v>22.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>19.8</v>
+        <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4236,7 +4233,7 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>72162.8</v>
+        <v>51.8</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>18.3</v>
@@ -4244,14 +4241,14 @@
       <c r="M46" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="N46" s="8" t="n">
-        <v>54.9</v>
+      <c r="N46" s="3" t="n">
+        <v>51.1</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>17.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>27.5</v>
@@ -4259,8 +4256,8 @@
       <c r="R46" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="8" t="n">
-        <v>19.8</v>
+      <c r="S46" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>53</v>
@@ -4281,7 +4278,7 @@
         <v>3.6</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>27.8</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>28.6</v>
@@ -934,7 +934,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>58.3</v>
+        <v>56.3</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -1004,7 +1004,7 @@
         <v>19.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
@@ -1069,7 +1069,7 @@
         <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
@@ -1087,7 +1087,7 @@
         <v>17.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>4</v>
@@ -1191,7 +1191,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>12.7</v>
+        <v>127.2</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>97.40000000000001</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1283,7 +1283,7 @@
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.4</v>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>28.2</v>
@@ -1490,7 +1490,7 @@
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>17.6</v>
@@ -1641,7 +1641,7 @@
         <v>17.8</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11</v>
@@ -1732,7 +1732,7 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.2</v>
+        <v>84.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
@@ -1783,7 +1783,7 @@
         <v>95.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>2</v>
+        <v>302</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>61</v>
@@ -1861,13 +1861,13 @@
         <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>15.7</v>
+        <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>22.2</v>
+        <v>120.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>254.1</v>
+        <v>902.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>30.4</v>
@@ -1946,10 +1946,10 @@
         <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>20.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>58</v>
@@ -1975,7 +1975,7 @@
         <v>17.8</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>11.8</v>
@@ -2032,7 +2032,7 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>54</v>
+        <v>28.2</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>30.6</v>
@@ -2176,7 +2176,7 @@
         <v>2.8</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>20</v>
@@ -2288,7 +2288,7 @@
         <v>76</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>145.6</v>
@@ -2313,7 +2313,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>56.2</v>
@@ -2436,19 +2436,19 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>2.2</v>
+        <v>13.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>11.7</v>
+        <v>24.7</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>18.4</v>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>22.8</v>
@@ -2483,7 +2483,7 @@
         <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12</v>
+        <v>19.6</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2564,7 +2564,7 @@
         <v>11.6</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
@@ -2643,7 +2643,7 @@
         <v>17.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>27.4</v>
@@ -2734,13 +2734,13 @@
         <v>9.4</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
         <v>474.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
@@ -2947,7 +2947,7 @@
         <v>71.59999999999999</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>9.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>0.7</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>26.6</v>
@@ -2997,16 +2997,16 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>5.1</v>
+        <v>25.6</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>3</v>
@@ -3021,10 +3021,10 @@
         <v>20.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.8</v>
+        <v>59.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.4</v>
+        <v>14.2</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>23.6</v>
@@ -3036,7 +3036,7 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>18</v>
@@ -3074,7 +3074,7 @@
         <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>7.2</v>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="n">
@@ -3110,10 +3110,10 @@
         <v>449.1</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>912.2</v>
+        <v>9119.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>1.5</v>
+        <v>26.2</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>14.6</v>
@@ -3178,7 +3178,7 @@
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>56</v>
@@ -3297,7 +3297,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D35" s="3" t="n">
         <v>24.2</v>
       </c>
@@ -3314,7 +3316,7 @@
         <v>16.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
@@ -3462,7 +3464,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>132.8</v>
@@ -3507,10 +3509,10 @@
         <v>133.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>162.2</v>
+        <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>101.7</v>
+        <v>218.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>288.6</v>
@@ -3522,10 +3524,10 @@
         <v>109.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>250.1</v>
+        <v>95</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>14.3</v>
+        <v>1014.3</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>86</v>
@@ -3560,7 +3562,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>1.7</v>
+        <v>17</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.2</v>
@@ -3582,7 +3584,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.9</v>
+        <v>29.9</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>26.8</v>
@@ -3606,13 +3608,13 @@
         <v>11.1</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>88.8</v>
+        <v>21.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3792,7 +3794,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>25.4</v>
@@ -3810,7 +3812,7 @@
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3843,13 +3845,13 @@
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.5</v>
+        <v>62.2</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>16.8</v>
@@ -3858,7 +3860,7 @@
         <v>17.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
@@ -3882,7 +3884,7 @@
         <v>16</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>12.6</v>
@@ -3900,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>18.4</v>
+        <v>17.4</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>15.8</v>
@@ -3965,7 +3967,7 @@
         <v>15</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>15.4</v>
@@ -3998,16 +4000,16 @@
         <v>3</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>20.4</v>
+        <v>30.4</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>42.6</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>25</v>
@@ -4041,25 +4043,25 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>15.3</v>
@@ -4077,13 +4079,13 @@
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>82</v>
+        <v>298.6</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>4</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>20.6</v>
+        <v>30.6</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>21.8</v>
@@ -4126,7 +4128,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>167.8</v>
@@ -4147,7 +4149,7 @@
         <v>33.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>9.4</v>
@@ -4159,10 +4161,10 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>99</v>
+        <v>499</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
@@ -4174,10 +4176,10 @@
         <v>121</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>115.2</v>
+        <v>116.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>17.9</v>
+        <v>317.9</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>107.1</v>
@@ -4189,7 +4191,7 @@
         <v>115</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>93.5</v>
+        <v>393.6</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>64.40000000000001</v>
@@ -4233,7 +4235,7 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>51.8</v>
+        <v>280.8</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>18.3</v>
@@ -4242,13 +4244,13 @@
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>51.1</v>
+        <v>2011</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.7</v>
+        <v>26.2</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>27.5</v>
@@ -4278,7 +4280,7 @@
         <v>3.6</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>27.8</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>28.6</v>
@@ -934,7 +934,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>56.3</v>
+        <v>58.3</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -1004,7 +1004,7 @@
         <v>19.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
@@ -1069,7 +1069,7 @@
         <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
@@ -1087,7 +1087,7 @@
         <v>17.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>31</v>
+        <v>31.8</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>4</v>
@@ -1182,7 +1182,7 @@
         <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>122.6</v>
+        <v>102.6</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>255.1</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1283,7 +1283,7 @@
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>20</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.4</v>
@@ -1383,13 +1383,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>23.1</v>
@@ -1641,7 +1641,7 @@
         <v>17.8</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>138.8</v>
@@ -1732,7 +1732,7 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>84.2</v>
+        <v>89.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
@@ -1834,7 +1834,7 @@
         <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>3.4</v>
@@ -1861,13 +1861,13 @@
         <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>19.7</v>
+        <v>10.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>120.1</v>
+        <v>22</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>902.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>30.4</v>
@@ -1946,10 +1946,10 @@
         <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>16.2</v>
+        <v>28.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>58</v>
@@ -2032,7 +2032,7 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>28.2</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16</v>
@@ -2288,7 +2288,7 @@
         <v>76</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>145.6</v>
@@ -2418,10 +2418,10 @@
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>25.4</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
@@ -2436,7 +2436,7 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>18.3</v>
@@ -2448,13 +2448,13 @@
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>22.8</v>
@@ -2483,7 +2483,7 @@
         <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>19.6</v>
+        <v>10</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>27.4</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>27.4</v>
@@ -2740,7 +2740,7 @@
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
         <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>13.2</v>
@@ -2902,7 +2902,7 @@
         <v>474.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>22</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>26.6</v>
@@ -3021,10 +3021,10 @@
         <v>20.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.2</v>
+        <v>59.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>23.6</v>
@@ -3036,7 +3036,7 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>17.2</v>
+        <v>57.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>18</v>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>29</v>
+        <v>20.8</v>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="n">
@@ -3110,10 +3110,10 @@
         <v>449.1</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>9119.1</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>26.2</v>
+        <v>2</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>14.6</v>
@@ -3178,7 +3178,7 @@
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>56</v>
@@ -3297,9 +3297,7 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="3" t="n">
         <v>24.2</v>
       </c>
@@ -3470,7 +3468,7 @@
         <v>132.8</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>882.1</v>
+        <v>88.2</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>11</v>
@@ -3512,7 +3510,7 @@
         <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>218.8</v>
+        <v>101.7</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>288.6</v>
@@ -3527,7 +3525,7 @@
         <v>95</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>1014.3</v>
+        <v>1.4</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>86</v>
@@ -3584,7 +3582,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>29.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>26.8</v>
@@ -3596,7 +3594,7 @@
         <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
@@ -3605,13 +3603,13 @@
         <v>22</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>11.1</v>
+        <v>5</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>11.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>21.8</v>
@@ -3720,7 +3718,7 @@
         <v>18.4</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>7.8</v>
@@ -3765,7 +3763,7 @@
         <v>57.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.4</v>
+        <v>14.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20.8</v>
@@ -3794,7 +3792,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>25.4</v>
@@ -3812,7 +3810,7 @@
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3845,7 +3843,7 @@
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.2</v>
+        <v>62.8</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>10.4</v>
@@ -3860,7 +3858,7 @@
         <v>17.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.2</v>
+        <v>76.5</v>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
@@ -4018,7 +4016,7 @@
         <v>26.4</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>19.6</v>
@@ -4043,7 +4041,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>30.6</v>
@@ -4058,7 +4056,7 @@
         <v>14.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>15.2</v>
+        <v>18.8</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>7.6</v>
@@ -4079,7 +4077,7 @@
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>298.6</v>
+        <v>84</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>4</v>
@@ -4112,7 +4110,7 @@
         <v>14.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4128,7 +4126,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>167.8</v>
@@ -4149,7 +4147,7 @@
         <v>33.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.2</v>
+        <v>61.5</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>9.4</v>
@@ -4161,7 +4159,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>499</v>
@@ -4188,7 +4186,7 @@
         <v>143</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>115</v>
+        <v>115.8</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>393.6</v>
@@ -4235,7 +4233,7 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>280.8</v>
+        <v>20.8</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>18.3</v>
@@ -4244,13 +4242,13 @@
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>2011</v>
+        <v>200</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>26.2</v>
+        <v>17.5</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>27.5</v>
